--- a/output/research_sample.xlsx
+++ b/output/research_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,29 +660,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Брюки классические прямые со стрелками</t>
+          <t>Брюки прямые чинос слаксы</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>159158694</v>
+        <v>8317220</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>Westrenger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>WESTRENGER</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/159158694/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/8317220/detail.aspx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -698,29 +698,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Брюки классические прямые</t>
+          <t>Брюки чиносы весенние классические прямые</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>147811028</v>
+        <v>17596354</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>Westrenger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>WESTRANGER</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/147811028/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/17596354/detail.aspx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -736,29 +736,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Брюки классические широкие со стрелками с защипом</t>
+          <t>Костюм классический двойка серый в офис смокинг на свадьбу</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3615932</v>
+        <v>147499497</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>STENSER</t>
+          <t>PAOLO MARK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>STENSER</t>
+          <t>Paolo Mark</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/3615932/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/147499497/detail.aspx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -774,29 +774,29 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Костюм классический свадебный тройка</t>
+          <t>Жилетка утепленная безрукавка с карманами</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155820791</v>
+        <v>201057687</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>Eberron</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>Eberron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/155820791/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/201057687/detail.aspx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -812,29 +812,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Брюки прямые чинос слаксы</t>
+          <t>Классический деловой костюм двойка</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8317220</v>
+        <v>412630283</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Westrenger</t>
+          <t>RIERA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WESTRENGER</t>
+          <t>Riera</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/8317220/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/412630283/detail.aspx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -850,29 +850,29 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Костюм классический деловой двойка</t>
+          <t>Костюм двойка классический деловой на свадьбу и мероприятие</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39410653</v>
+        <v>5346719</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STENSER</t>
+          <t>ABSOLUTEX</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>STENSER</t>
+          <t>BAZI FASHION GROUP</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/39410653/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/5346719/detail.aspx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -888,29 +888,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Классический костюм оверсайз двойка</t>
+          <t>Пиджак классический синий</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>183645701</v>
+        <v>224156417</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>Henry Lannister</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>Henry Lannister</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/183645701/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/224156417/detail.aspx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -926,29 +926,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Брюки чиносы весенние классические прямые</t>
+          <t>Костюм двойка классический свадебный</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17596354</v>
+        <v>28965863</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Westrenger</t>
+          <t>Daniel Diaz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WESTRANGER</t>
+          <t>ИП Пантелеев Максим Сергеевич</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/17596354/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/28965863/detail.aspx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Костюм классический двойка серый в офис смокинг на свадьбу</t>
+          <t>Костюм классический тройка смокинг свадебный черный</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>147499497</v>
+        <v>336261543</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PAOLO MARK</t>
+          <t>Paolo Marni</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paolo Mark</t>
+          <t>Paolo Marni</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/147499497/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/336261543/detail.aspx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1002,29 +1002,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Жилетка утепленная безрукавка с карманами</t>
+          <t>Костюм смокинг классический тройка на свадьбу черный</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>201057687</v>
+        <v>420298393</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eberron</t>
+          <t>Paolo Marni</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eberron</t>
+          <t>PM SHOP</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/201057687/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/420298393/detail.aspx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1040,29 +1040,29 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Брюки классические прямые со стрелками</t>
+          <t>Брюки бананы классические</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>348349668</v>
+        <v>168802669</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>BEND</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SUITBASE</t>
+          <t>BEND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/348349668/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/168802669/detail.aspx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>412630283</v>
+        <v>418131232</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RIERA</t>
+          <t>CALM FEAR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riera</t>
+          <t>CALM FEAR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/412630283/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/418131232/detail.aspx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1116,29 +1116,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Брюки чиносы прямые классические слаксы</t>
+          <t>Костюм классический двойка пиджак и брюки</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17596351</v>
+        <v>446684570</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Westrenger</t>
+          <t>СВОИ ЛЮДИ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WESTRANGER</t>
+          <t>СВОИ ЛЮДИ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/17596351/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/446684570/detail.aspx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1154,29 +1154,29 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Костюм тройка синий деловой повседневный</t>
+          <t>Свитер полузамок с горлом вязаный теплый джемпер на молнии</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>230232911</v>
+        <v>453417153</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LACONI</t>
+          <t>Pancake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BAZI FASHION GROUP</t>
+          <t>Чайковская Н.А</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/230232911/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/453417153/detail.aspx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1192,29 +1192,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Брюки классические прямые чинос слаксы</t>
+          <t>Брюки классические широкие укороченные бананы со стрелками</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14273996</v>
+        <v>536099206</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Westrenger</t>
+          <t>OUTSWAY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WESTRENGER</t>
+          <t>Магазин продавца</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/14273996/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/536099206/detail.aspx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1230,29 +1230,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Костюм двойка классический деловой на свадьбу и мероприятие</t>
+          <t>Брюки мужские классические</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5346719</v>
+        <v>441476155</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABSOLUTEX</t>
+          <t>SURVILON</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZI FASHION GROUP</t>
+          <t>ПОСМОТРЕТЬ ВСЕ ТОВАРЫ СО СКИДКОЙ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/5346719/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/441476155/detail.aspx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Пиджак классический синий</t>
+          <t>Костюм классический двубортный деловой</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>224156417</v>
+        <v>444439656</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Henry Lannister</t>
+          <t>BENSO_BRAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Henry Lannister</t>
+          <t>Benso_Brand</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/224156417/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/444439656/detail.aspx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1306,29 +1306,29 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Классический свадебный костюм тройка</t>
+          <t>Костюм классический тройка смокинг свадебный черный</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>296160659</v>
+        <v>591129737</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>Paolo Marni</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TOMMY HAAS</t>
+          <t>PAOLO STYLE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/296160659/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/591129737/detail.aspx</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1344,29 +1344,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Костюм двойка классический свадебный</t>
+          <t>Костюм классический тройка деловой</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28965863</v>
+        <v>458480139</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Daniel Diaz</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ИП Пантелеев Максим Сергеевич</t>
+          <t>Ramazotti</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/28965863/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/458480139/detail.aspx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1382,29 +1382,29 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Классический деловой мужской костюм тройка на свадьбу и офис</t>
+          <t>Костюм двойка деловой больших размеров</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11518058</v>
+        <v>195997730</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LACONI</t>
+          <t>HALF HORSE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BAZI FASHION GROUP</t>
+          <t>ИП Пантелеев Максим Сергеевич</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/11518058/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/195997730/detail.aspx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1420,29 +1420,29 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Брюки классические прямые чинос</t>
+          <t>Брюки классические со стрелками оверсайз на резинке</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13511021</v>
+        <v>195747703</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Westrenger</t>
+          <t>zyone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WESTRENGER</t>
+          <t>ZYONE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/13511021/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/195747703/detail.aspx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1458,29 +1458,29 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Костюм классический тройка смокинг свадебный черный</t>
+          <t>Брюки бананы классические со стрелками</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>336261543</v>
+        <v>535233688</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paolo Marni</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paolo Marni</t>
+          <t>TOOG Brand</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/336261543/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/535233688/detail.aspx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1496,29 +1496,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Костюм смокинг классический тройка на свадьбу черный</t>
+          <t>Брюки классические со стрелками бананы</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>420298393</v>
+        <v>234282939</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paolo Marni</t>
+          <t>RAZNЫЙ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PM SHOP</t>
+          <t>Магазин</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/420298393/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/234282939/detail.aspx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1534,29 +1534,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Костюм мужской классический двойка в офис свадьба</t>
+          <t>Брюки карго прямые с карманами хлопок</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>473605897</v>
+        <v>152239380</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paolo Marni</t>
+          <t>TACTICAL FROG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paolo Marni</t>
+          <t>TACTICAL FROG</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473605897/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/152239380/detail.aspx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1572,32 +1572,8886 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Костюм классический двойка голубой в офис смокинг на свадьбу</t>
+          <t>Костюм двойка брючный</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>147499501</v>
+        <v>263748039</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Klife</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Klife</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/263748039/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>99</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Костюм вельветовый тройка без начеса</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>463612587</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TM LIMITED</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MEN'S WEAR</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/463612587/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>102</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Костюм мужской классический двойка приталенный</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13865734</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TRUVOR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BYDAY WEAR</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/13865734/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>106</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Брюки бананы классические со стрелками</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>297160065</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ТрендМэн</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ТрендМэн</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/297160065/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>110</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Брюки бананы классические со стрелками</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>244557554</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JETTI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ИП Шин Наталья Феофановна</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/244557554/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>114</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые в офис</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>316635459</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>МАЯКОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ТМ Маяковский</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/316635459/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>116</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Костюм тройка классический свадебный деловой</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>119316414</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DANIEL GALLOTTI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DENIM ELATION</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/119316414/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>119</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>костюм повседневный в стиле OLD MONEY</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>215372385</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Martin wear</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/215372385/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>120</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Костюм классический тройка смокинг на свадьбу черный</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>150000211</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Daniel tussi</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Daniel Tussi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/150000211/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>121</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Костюм классический тройка деловой</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>535286080</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ELEGANZO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>KaKetKa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/535286080/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>123</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Джоггеры штаны зауженные на резинке свободные</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>137968363</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Milton Jeans</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tip Top Brand</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/137968363/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>125</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>214877686</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Black Z</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BLACK Z</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/214877686/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>135</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Классический костюм двойка</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>317382338</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MONLARTI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Магазин одежды и аксессуаров MONLARTI</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/317382338/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>136</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>172138519</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GENTFIT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gentfit</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/172138519/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>139</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Пиджак классический из премиальной итальянской 100% шерсти</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>340392585</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BAZIONI</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/340392585/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>141</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Пиджак классический под джинсы в офис повседневный</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>589936977</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>PAOLO MARK</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PAOLO STYLE</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/589936977/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>152</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Костюм льняной летний повседневный</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>208962264</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Albasetter</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Albasetter</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/208962264/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>155</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>556838055</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DREAMVIBE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DREAMVIBE</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/556838055/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>156</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Брюки чиносы классические прямые</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>218834738</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>WST Wave. Style. Time.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>WST Wave. Style. Time.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/218834738/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>157</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>329621292</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Manterra</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ИП Мещерский Г.Г.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/329621292/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>161</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Пиджак оверсайз под джинсы повседневный классический</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>197887291</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FarReaching</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FarReaching</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/197887291/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>163</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы кэжуал</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>101818693</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>VipDressCode</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>VIPDRESSCODE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/101818693/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>164</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Пиджак классический под джинсы повседневный</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>342767164</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EMOR</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>EMOR Boutique</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/342767164/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>165</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Повседневный костюм спортивный на молнии двойка</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>103224127</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BRAIBO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Качественная мужская одежда по выгодным ценам</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/103224127/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>172</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие со стрелками</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>227495120</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ludi</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>LUDI</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/227495120/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>173</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Пиджак классический черный приталенный</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>318205478</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ZINTO suit</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>UMALO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/318205478/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>175</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>классический свадебный костюм тройка</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>435718944</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DANIEL HAZARD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DANIEL HAZARD</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/435718944/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>179</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Костюм классический прямой на праздник</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>724584438</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ARGO MEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Argo BY</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/724584438/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>184</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Костюм классический трикотажный елочка</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>248673443</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RICHARDSON</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>RICHARDSON smart casual</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/248673443/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>189</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Пиджак классический в клетку под джинсы</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>338517432</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ZORIN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZORIN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/338517432/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>190</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые в офис</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>90466699</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>HILL HARMONIUMWILL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HILL HARMONIUMWILL</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/90466699/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>193</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Костюм тройка классический в клетку свадебный</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>292971256</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DENIM ELATiON</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DENIM ELATION</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/292971256/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>195</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Пиджак мужской под джинсы повседневный классический черный</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>168918040</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PAOLO LUX</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PAOLO LUX</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/168918040/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>203</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные к низу прямые в офис</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>95593471</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AVZ FASHION</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AVZ Fashion</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/95593471/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>204</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные чинос</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>174547019</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CASUAL CLUB</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CASUAL CLUB</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/174547019/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>211</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Костюм теплый вельветовый весенний old money</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>436688670</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TM LIMITED</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TM LIMITED</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/436688670/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>213</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Рубашка классическая приталенная с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>101671344</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>A.Moretti</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>7 Brands</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/101671344/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>215</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>229639363</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NØN - now or never</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>VORONOV STORE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/229639363/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>217</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Брюки зауженные повседневные джоггеры с карманами карго</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11799179</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Street Spirit</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>street spirit</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/11799179/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>220</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Мужская рубашка с длинным рукавом на кнопках приталенная</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>153909182</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Дисконт</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ДИСКОНТ</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/153909182/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>230</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы оверсайз</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>309180330</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>QARIM</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/309180330/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>237</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>250651528</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Style Driven</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ООО Текстиль 24</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/250651528/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>244</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Кардиган на молнии</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>178453836</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ALFOMEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ALL FOR MEN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/178453836/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>248</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Брюки вельветовые черные</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>195847314</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>qhuse</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>qhuse</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/195847314/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>249</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>336278205</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ART FAMILY</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ART FAMILY</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/336278205/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>258</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы трикотажный классический</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>262141861</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>asfashiondp</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ASFASHIONDP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/262141861/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>263</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы повседневный классический</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>239487457</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DANiEL MAXi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Studio 123 - одежда для яркой жизни</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/239487457/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>264</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>279877600</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Koutons</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ковбой</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/279877600/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>275</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Рубашка без воротника с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>122971700</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cassa Marina</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CASSA MARINA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/122971700/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>279</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом на кнопках с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>391045690</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Paul Star</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PROMISED SAVIOUR</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/391045690/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>281</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Рубашка тактическая на кнопках с карманами</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>159639581</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TACTICAL FROG</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FROG BREND</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/159639581/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>283</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Пиджак вельветовый под джинсы темно синий</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>455684570</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Goodman</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Henry Lannister</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/455684570/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>284</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Джемпер мужской Турция кофта поло больших размеров тонкий</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>662929788</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Cracow</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JE LA PECHE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/662929788/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>293</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Муслиновая рубашка с длинным рукавом воротник стойка</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>95849540</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Country Stories</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Country Stories</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/95849540/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>295</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Брюки бананы классические мужские со стрелками на выпускной</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>296002810</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Melonea</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gosobr</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/296002810/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>296</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Брюки джоггеры хлопок зауженные с карманами</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>145181324</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>HITFORMA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>HITFORMA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/145181324/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>298</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>204945872</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>INSANWEAR</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>INSANWEAR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/204945872/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>300</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Брюки базовые прямые со стрейчем большие размеры</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>484471686</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>TOM TAILOR</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tom Tailor - официальный интернет-магазин</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/484471686/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>314</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Пиджак классический в клетку повседневный под джинсы</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>346648818</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Maiestas</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Maiestas</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/346648818/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>317</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>52278903</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>GANZEL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>GANZEL</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/52278903/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>320</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые широкие оверсайз на резинке</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>277231411</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Baron</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ООО КУРСИВ</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/277231411/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>321</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Костюм классический тройка синий в офис смокинг на свадьбу</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>430243789</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PAOLO STYLE</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>PM SHOP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/430243789/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>326</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Джемпер на молнии классический однотонный кофта на замке</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>188483333</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>KASTA 7</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>KASTA 7</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/188483333/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>344</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Жилетка мужская весна-осень утепленная</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>330946881</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Easy Yard</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Easy Yard</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/330946881/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>347</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Плиссированные оверсайз-брюки широкие костюмные</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>483600021</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Диагональ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Дунбэй</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/483600021/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>362</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Костюм мужской с гербом России</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>815276178</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SKULL LOFT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SKULL LOFT</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/815276178/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>368</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Пиджак</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>330136071</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ISION</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/330136071/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>373</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>345057513</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KAW</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KAW</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/345057513/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>374</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы повседневный оверсайз классический</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>403727941</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Line 17</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Line 17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/403727941/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>377</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>14357443</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AxLer</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AxLer</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/14357443/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>379</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Рубашка без воротника с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>170181975</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>BASIO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BASIO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/170181975/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>381</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Брюки чиносы зауженные летние легкие классика</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>144711811</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PKAS CLASSIC</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PKAS CLASSIC</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/144711811/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>382</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Костюм двойка повседневный классический</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>212431535</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Essentials Minnim</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Essentials Minnim</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/212431535/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>385</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Брюки мужские классические коричневые бананы</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>604098173</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>COM&amp;DIR</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NASYR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/604098173/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>389</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>08. Оверсайз костюм брючный классический.</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>498082105</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Rich One</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Rich One Эксклюзив!</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/498082105/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>391</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Костюм ВКПО военный уставной тактический</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>585603668</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ЗАЩИТА И ОБОРОНА</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ЗАЩИТА И ОБОРОНА</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/585603668/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>395</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Классические брюки не требующие глажки, с Легким уходом!</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>113155502</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>kiyim</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>kiyim</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/113155502/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>399</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Вельветовый костюм с бомбером и брюками</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>693450082</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AF LIMITED</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ИП Гогуева А. А.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/693450082/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>404</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом приталенная классическая</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>254771582</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OUUMA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>OUUMA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/254771582/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>420</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Брюки джоггеры Школа</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>175924761</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>JOGGBERRY</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JOGGBERRY</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/175924761/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>426</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Брюки спортивные прямые Трико летнее</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3892654</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LAINA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>LAINA &amp; STELLIO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/3892654/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>429</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые со стрелкой</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>437310765</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Bocu</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bocu</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/437310765/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>436</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом приталенная</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>253599185</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>D&amp;U mens</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>D&amp;U mens</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/253599185/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>437</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>574113691</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>bySR</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>bySR</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/574113691/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>440</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>188207534</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>HAMILLS</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HAMILLS</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/188207534/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>443</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>пиджак трендовый</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>218746928</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ISION</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ISION</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/218746928/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>445</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Костюм Полиция форменный тк. Патруль</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>489689651</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Кавказ Форма</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Кавказ Форма</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/489689651/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>446</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Костюм двойка классический свадебный деловой</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>411178983</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Zinto Collection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Zinto collection</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/411178983/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>447</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Брюки классические</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>74038536</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NANSEN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Nansen</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/74038536/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>468</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Пиджак классический прямой</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>206715848</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Kld man</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gentleman</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/206715848/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>469</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Костюм классический мужской тройка</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>214985558</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Men's Factor</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Alfa</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/214985558/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>475</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом летняя хлопок стойка белая</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>149733474</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Муслиновые рубашки EFES Premium</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Качественные Мужские Рубашки</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/149733474/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>480</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Брюки классические на резинке прямые зауженные со стрелками</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>190819892</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>lipkinof</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>lipkinof</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/190819892/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>482</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые в офис школу</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>254977058</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PLANETA JEANS</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>PLANETA jeans</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/254977058/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>483</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Джоггеры брюки карго с карманами черные</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>264030567</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>HOODRICH</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Dermaheal Korea</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/264030567/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>486</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Брюки вельветовые классические</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>249646683</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Carlo space</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Supreme jeans</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/249646683/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>493</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Рубашка оверсайз с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>328061089</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>FANBOX</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FANBOX</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/328061089/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>502</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Брюки широкие классические прямые</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>436988523</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Диагональ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>СКОРОСТЬ</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/436988523/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>503</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Пиджак в клетку темно синий под джинсы классический</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>150663959</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Antonio Vicci</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Antonio Vicci</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/150663959/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>506</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Костюм тройка классический смокинг</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>27137742</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PROFER</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>profer</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/27137742/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>513</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Рубашка с коротким рукавом летняя</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>709610007</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DS-БЕРА</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>БЕРА</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/709610007/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>514</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом классическая полуприталенная</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>482977476</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>serotonin</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Serotonin</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/482977476/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>516</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Чёрный костюм с брюками и рубашкой</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>615749241</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Korsakov</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Korsakov</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/615749241/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>517</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Вельветовые брюки в рубчик классические</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>337441977</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MEGA JEANS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>MEGA JEANS</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/337441977/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>525</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие бананы</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>561515328</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Darya Selskaya</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DARYA SELSKAYA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/561515328/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>527</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Джемпер Кардиган на молнии шерстяной</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>222291094</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>YAMAK</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>YAMAK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/222291094/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>529</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Брюки классические весенние прямые на резинке</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>493823243</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TANIRI</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/493823243/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>532</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Брюки широкие багги шаровары парашюты y2k биг бои sk8 3pm</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>433902573</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RIMILLI</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>RIMILLI</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/433902573/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>533</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы повседневный оверсайз молодежный</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>163915644</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>InTravel</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>InTravel</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/163915644/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>534</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Пиджак классический приталенный повседневный под джинсы</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>200475838</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NATA ZAR</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>NATA ZAR</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/200475838/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>540</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом оверсайз в полоску</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>539871207</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>TENSEI</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>TENSEI</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/539871207/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>541</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Оверсайз рубашка с принтом плотная</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>110253111</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>SUN Street</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ГРАДИЕНТ</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/110253111/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>544</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Жилетка с воротником безрукавка демисезонная утепленная</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>488199757</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Q-Lin</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Q-Lin</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/488199757/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>545</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Костюм мужской летний вельветовый комплект штаны и рубаха</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>209467536</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SUNWERT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SUNWERT</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/209467536/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>550</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом на кнопках и отложным воротником</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>742763503</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Belt&amp;Buttons</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Маркет Партнер</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/742763503/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>551</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Джемпер свитер кофта мужской тонкий Турция</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>173878157</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>L, ONN</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Верный Крой</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/173878157/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>553</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные чиносы</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>321876558</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>L.A.F</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>L.A.F</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/321876558/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>559</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Оверсайз спортивные штаны свага y2k</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>463521378</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Tishka</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ИП Кочергин М. Д.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/463521378/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>561</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Рубашка белая оверсайз с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>243637402</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Blackpires</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>BLACKPIRES</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/243637402/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>568</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Брюки классические зауженные чиносы на резинке</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>485379179</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>LINESIDE</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>LINESIDE</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/485379179/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>569</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Мужская рубашка с воротником-стойкой</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>453843625</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Zolla</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Zolla</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/453843625/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>570</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Костюм классический</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>492447915</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Martino Castelly</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Martino Castelly</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/492447915/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>573</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Брюки джинсы больших размеров на резинке</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>247190557</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BIG HILL</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>BIG</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/247190557/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>581</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>264831132</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MYVIBE</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MYVIBE</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/264831132/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>582</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками оверсайз</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>227830448</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>BARSI</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>barsi</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/227830448/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>597</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Широкие Брюки спортивные оверсайз палаццо джоггеры</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>445249347</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Диагональ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Диагональ</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/445249347/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>605</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Брюки черные классические прямые</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>310287349</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ZORLEN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Zorlen</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/310287349/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>608</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Пиджак классический повседневный под джинсы</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>447855317</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Max Krause</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Max Krause</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/447855317/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>612</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Брюки со стрелками классические широкие бананы оверсайз</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>371324529</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>GSH style</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Дом Гончаровых</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/371324529/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>622</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Рубашка в полоску</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>304051165</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Chilandge</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Chilandge</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/304051165/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>624</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Джемпер мужской на весну</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>669118243</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>KappuSheFF</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>KappuSheFF</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/669118243/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>625</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Костюм в полоску на полузамке осенний с брюками хлопок</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>469592264</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Rэv</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Rэv</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/469592264/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>635</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Классическая рубашка с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>117572139</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>A S Y</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Маркет Партнер</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/117572139/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>638</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Джемпер классический кофта премиум качества</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>194989076</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>STANFORT</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/194989076/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>641</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы в клетку повседневный классический синий</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>549160404</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PAOLO MARK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>VELOGO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/549160404/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>644</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Пиджак оверсайз повседневный под джинсы</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>263393969</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Jany Dem</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JANY DEM</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/263393969/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>651</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Рубашка мужская с длинным рукавом классическая белая</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>88737941</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AMTER</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>AMTER</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/88737941/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>653</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Кардиган накидка</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>6532970</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Envy Lab</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Envy Lab</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/6532970/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>656</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Рубашка теплая с длинным рукавом в клетку</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>254906007</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>SHAMBI</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FAA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/254906007/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>657</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Вельветовые брюки классические на резинке</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>263885835</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Cotta</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Vera Nicco</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/263885835/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>661</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Классический пиджак под джинсы повседневный</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>480204885</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>BREEZY MAN</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>БРИЗИ МЕН</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/480204885/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>663</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Костюм классический двойка</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>369102590</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Kristall</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>KRISTALL</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/369102590/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>667</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие бананы</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>548740302</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>DreamFit</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>DREAMFIT</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/548740302/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>679</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Брюки со стрелками классические</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>412752503</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>A'MEN</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>A'MEN</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/412752503/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>682</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Офисная форма МО военная</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>333427329</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Полигон</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ПОЛИГОН</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/333427329/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>683</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>456666470</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>YStaler</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>YSTALER</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/456666470/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>685</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые летние</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>21256129</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>DITE</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ЕОА</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/21256129/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>694</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом классическая</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>676654542</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>MirSer</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Passion&amp;FashionMEN</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/676654542/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>695</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Брюки Гуркха широкие с высокой талией</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>32683444</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Maden. Amekaji wear.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Maden. Amekaji Wear. Red Tornado. SAUCE ZHAN</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/32683444/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>697</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Брюки свободные y2k оверсайз</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>133818124</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Kristian White</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Kristian White</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/133818124/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>701</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Костюм мужской тройка классический приталенный</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>529950732</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>DIMARK</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>DIMARK</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/529950732/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>702</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Пиджак оверсайз классический</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>612323791</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>BANKOL</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>BANKOL/SHWЭDAR</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/612323791/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>727</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Джемпер поло old money с длинным рукавом, хлопок. Турция</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>247271788</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Cahoter</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>MODERNO</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/247271788/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>732</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Костюм двойка вельветовый (OLD MONEY)</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>505447290</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Faccia</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>FACCIA</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/505447290/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>733</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом хлопок</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>150414836</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Platon</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Platon</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/150414836/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>741</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Рубашка джинсовая с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>63994126</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>My Boss</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>PREMIUM QUALITY</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/63994126/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>744</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>210344596</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>PERFECTEKA</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ИП Кублицкая Е.И.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/210344596/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>747</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Брюки классические теплые на резинке</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>253929503</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SMITLEN</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>SMITLEN</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/253929503/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>749</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Пиджак под джинсы на пуговицах трикотажный</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>119233399</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Bartolomeo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ИП Юнис Ольга Владимировна</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/119233399/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>752</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Костюм двубортный классический</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>554014722</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>CaesarLeo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>CaesarLeo</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/554014722/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>754</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом полуприталенная классическая</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>468671050</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Malone Club</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>5Label - Where Heritage Meets Hype</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/468671050/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>757</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Брюки бананы со стрелками укороченный</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>252681413</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ToP MaStEr</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Топ Мастер</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/252681413/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>758</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Жилетка утепленная демисезонная</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>321213279</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Iron Mark</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Iron Mark</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/321213279/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>759</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом приталенная на кнопках</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>452288844</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Virilitas</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>VIRILITAS</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/452288844/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>760</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Пиджак оверсайз повседневный под джинсы классический в офис</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>189790254</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Paolo Marni</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>Paolo Mark</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/147499501/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/189790254/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>763</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Пиджак офисный слим фит под джинсы</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>150864707</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>DJ PLUS</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>BAD BOYS</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/150864707/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>764</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Костюм повседневный с брюками</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>462957927</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>BLACKSUS</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>blacksus</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/462957927/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>767</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом классическая хлопок в полоску</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>400637532</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ALVY BRAND</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ALVY BRAND</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/400637532/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>770</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы прямые зауженные со стрелками</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>400758845</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>BAYE</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>KAIRO</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/400758845/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>771</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Брюки спортивные утепленные на резинке с начесом</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>41620875</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ТЕЛОДВИЖЕНИЯ</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ООО СКВТ</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/41620875/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>773</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Брюки классические полуприлегающие</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>239469808</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>HENDERSON</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>HENDERSON</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/239469808/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>777</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Рубашка классическая с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>144219497</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>OSSBORN</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>OSSBORN</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/144219497/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>778</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Джемпер поло тонкий классика длинный рукав</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>565114857</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>DEVINSTYLE</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>DEVINSTYLE</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/565114857/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>779</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Брюки классические мужские old money</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>274391602</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>GERVONT</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>GERVONT</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/274391602/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>780</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Брюки льняные летние прямые</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>158761708</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>DUCHO</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>DUCHO</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/158761708/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>791</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом на кнопках хлопок стойка черная</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>190449004</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Рубашки на кнопках</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Качественные Мужские Рубашки</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/190449004/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>793</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Рубашка мужская с длинным рукавом классическая</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>153383294</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>WеstНеrо (alazavr)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Alazavr</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/153383294/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>796</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Рубашка оверсайз вельветовая</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>190708927</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>SHEEFR</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SHEEFR</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/190708927/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>798</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Костюм двойка классический оверсайз</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>323165738</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Jake.Evl</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Jake.Evl</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/323165738/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>802</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Брюки вельветовые классические прямые плотные</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>587395033</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>VYBE</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>это СТИЛЬ</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/587395033/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>804</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Пиджак классический однобортный</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>440745988</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Befree</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>MELON FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/440745988/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>812</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Пиджак с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>145271454</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>STRICCLO</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>STRICCLO</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/145271454/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>816</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Пиджак классический оверсайз</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>246338728</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Nepiqee</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Nepiqee</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/246338728/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>817</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Брюки классические со стрелкой в офис и школу</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>429063623</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>MOTTON</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>MOTTON</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/429063623/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>821</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Рубашка льняная на кнопках с коротким рукавом</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>305504259</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>JOHN VARCO</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ДИСКОНТ</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/305504259/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>826</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>576045498</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Limiton</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Limiton</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/576045498/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>830</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом оверсайз хлопковая</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>178258605</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>KOSTTER</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>KOSTTER</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/178258605/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>832</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые со стрелками</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>13035205</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Linea QUALITEX</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>МИР-БРЮК ___ Linea QUALITEX</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/13035205/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>834</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Джемпер кардиган мужской на молнии на весну</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>251237378</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>NATTAK</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>NATTAK</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/251237378/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>838</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Рубашка приталенная классическая с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>134023800</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>MAYT</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>MAYT</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/134023800/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>840</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Костюм вельветовый с рубашкой</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>213420191</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>TM LIMITED</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Billions</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/213420191/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>841</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Кардиган вязаный на пуговицах поло</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>462556821</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>DOUX SAINT</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Каталог DOUX SAINT</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/462556821/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>845</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Брюки бананы классические со стрелками оверсайз</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>365732528</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Bayan</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Bayan</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/365732528/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>848</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом летняя льняная оверсайз</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>220840040</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>GlESTO</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>SHARM</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/220840040/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>852</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Рубашка микровельвет</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>117957184</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Essecco</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Essecco</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/117957184/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>858</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Рубашка классическая с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>180084779</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>OSSBORN WEAR</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>OSSBORN WEAR</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/180084779/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>860</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Костюм летний с брюками хлопок</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>241476647</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>OSSAM</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>OSSAM</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/241476647/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>861</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Брюки прямые широкие классические свободные</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>208348435</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Gizi</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Gizi wear</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/208348435/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>863</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Брюки джоггеры утепленные с флисом</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>178628338</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>BroJeans</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>BroJeans</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/178628338/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>866</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Пиджак классический под джинсы повседневный</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>64351338</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>MODCLICK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>MODCLICK</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/64351338/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>867</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Брюки багги широкие оверсайз y2k</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>598979404</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>VAER</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/598979404/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>870</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые со стрелками</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>146630050</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>CrewMenShop</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>crewmenshop, sokolov men shop</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/146630050/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>873</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Рубашка классическая с длинным рукавом праздничная</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>145058428</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Staros</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Staros</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/145058428/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>880</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Рубашка на кнопках приталенная Турция</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>179914538</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Le Valdo</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Le Valdo - То что подходит Вам.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/179914538/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>883</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Классический костюм повседневный кэжуал</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>521624807</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Burmistr</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>BURMISTR</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/521624807/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>885</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Рубашка льняная</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>32443841</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>PONOTE</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>PONOTE</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/32443841/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>892</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Рубашка классическая с длинным рукавом в полоску</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>268670060</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>APUI</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>AIWEAR</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/268670060/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>898</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>438872081</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>IO TREND</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>IO</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/438872081/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>904</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Пиджак повседневный классический под джинсы</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>233250695</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Jake.E</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Konkurent Povel'a</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/233250695/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>907</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Брюки джоггеры мужские с карманами на резинке</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>65714204</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>ARVADOR</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>СКИДКИ до 80%</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/65714204/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>908</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Брюки бананы классические легкие</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>168482282</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>TopYoungs</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>TopYoungs</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/168482282/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>910</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Рубашка Белая с длинным рукавом классическая</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>482211909</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>H&amp;Bold</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>H&amp;Bold</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/482211909/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>917</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Рубашка классическая с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>236295528</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Outfit4man</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>OUTFIT4MAN</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/236295528/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>928</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие с защипами</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>494434564</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>motivate</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>M8 motivate</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/494434564/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>930</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Рубашка мужская белая джинсовая с длинным рукавом на кнопках</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>176923639</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ZAKATNOVshop</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ZAKATNOVshop</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/176923639/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>939</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Премиум рубашка с длинным рукавом классическая хлопок</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>300568046</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Oh my man!</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>oh my man!</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/300568046/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>942</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Брюки спортивные трико</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>13269118</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Зари</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Зари. Мои Любимые брюки</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/13269118/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>948</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Джоггеры брюки чиносы карго на резинке</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>93998710</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>INYwear</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>INYwear GROUP</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/93998710/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>953</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Пиджак блейзер однотонный под джинсы повседневный</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>299770519</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aspit</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>ASPIT</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/299770519/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>955</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Брюки широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>321885105</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>NONAKED</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NONAKED</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/321885105/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>957</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Джемпер поло турция теплый на пуговицах кашемир</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>173415261</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>FORTUNELLY</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Passion&amp;FashionMEN</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/173415261/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>961</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Брюки джоггеры карго с карманами</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>169540884</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ICON BROTHERS</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Bronks</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/169540884/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>967</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Джемпер кофта свитер пуловер лонгслив свитшот тонкий хлопок</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>145857035</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>БРУТИС</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>БРУТИС</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/145857035/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>971</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Брюки со стрелками классические широкие бананы</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>253223313</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>UNYielding</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Владислав</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/253223313/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>978</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Брюки классические прямые в офис</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>209826093</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>OUTFITZ</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>OUTFITZ</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/209826093/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>981</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Рубашка габардин приталенная с длинным рукавом slim fit</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>214517281</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>BAGOTTI</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>BAGOTTI</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/214517281/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>982</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Брюки вельветовые широкие на резинке</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>183186005</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>VERHOVNIY</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>VERHOVNIY</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/183186005/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>985</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Брюки классические бананы со стрелками оверсайз</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>252558800</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>CLstyle</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>CLstyle</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/252558800/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>986</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Брюки классические широкие оверсайз</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>498897274</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Lu City</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Lu City</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/498897274/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>988</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Рубашка приталенная с длинным рукавом</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>497650840</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>GlESTO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>GIESTO</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/497650840/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>989</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Кардиган</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>118030110</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>AWANN</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ИП Минакова Анастасия Муанисовна</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/118030110/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>994</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Рубашка с длинным рукавом в полоску</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>454459234</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>MIGSON</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>MIGSON</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/454459234/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>995</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Жилетка утепленная демисезонная</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>492967867</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>MSO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/492967867/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>997</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Брюки карго джоггеры на высоких</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>230573515</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>dolo74</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>dolo74</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/230573515/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
         <is>
           <t>READY_FOR_RESEARCH</t>
         </is>

--- a/output/research_sample.xlsx
+++ b/output/research_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -474,25 +474,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном длинная</t>
+          <t>Видеокарта RTX 5070 12 ГБ RTL (RTX 5070 12G SHADOW 2X OC)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>502380099</v>
+        <v>355329855</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>La VIO</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>La VIO</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/502380099/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/355329855/detail.aspx</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -512,25 +512,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Куртка парка зимняя с капюшоном</t>
+          <t>Видеокарта RX 9070 XT Challenger</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>492302848</v>
+        <v>781591963</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SOFO</t>
+          <t>ASRock</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SOFO</t>
+          <t>Lumono</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/492302848/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/781591963/detail.aspx</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -550,25 +550,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Куртка весна с капюшоном удлиненная демисезонная</t>
+          <t>Видеокарта RTX 5070 Ti 16 ГБ RTL (GV-N507TWF3OCV2-16GD)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>144678759</v>
+        <v>706673918</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>STEFRIMI</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STEFRIMI</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/144678759/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/706673918/detail.aspx</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -588,25 +588,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Куртка женская демисезонная тонкая с капюшоном весна</t>
+          <t>Видеокарта для пк RTX 5070 12ГБ GDDR7 WINDFORCE OC SFF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>172327837</v>
+        <v>393771530</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DAYCLO</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DAYCLO</t>
+          <t>СИТИЛИНК</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/172327837/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/393771530/detail.aspx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -618,33 +618,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Куртка кожаная косуха весенняя</t>
+          <t>RTX 5090 TUF GAMING 32 ГБ (TUF-RTX5090-32G-GAMING)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>144680877</v>
+        <v>823111536</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gouter</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fashion Design</t>
+          <t>Продавец</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/144680877/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/823111536/detail.aspx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -656,33 +656,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная с капюшоном</t>
+          <t>Видеокарта RTX 5070 Twin Edge</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>203625366</v>
+        <v>784893688</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SHAYLY</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SHAYLY</t>
+          <t>Lumono</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/203625366/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/784893688/detail.aspx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -694,33 +694,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Куртка демисезонная стеганая удлиненная с капюшоном Пальто</t>
+          <t>RTX 5070 Ti GAMING TRIO OC 16 ГБ (RTX 5070 Ti 16G GAMING TRI…</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118177975</v>
+        <v>823110325</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VASHLOOK</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VASHLOOK</t>
+          <t>Продавец</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/118177975/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/823110325/detail.aspx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -732,33 +732,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Куртка</t>
+          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (NE7506TS19T1-GB2061S)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>185222392</v>
+        <v>527449656</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USEREZHI</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USEREZHI УСЕРЁЖИ</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/185222392/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/527449656/detail.aspx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -770,33 +770,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Куртка демисезонная стеганая</t>
+          <t>RTX 5070 Ti EAGLE OC ICE SFF 16 ГБ (GV-N507TEAGLEOC ICE-16GD)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155897954</v>
+        <v>565713653</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ООО МАГИЯПАЛЬТО</t>
+          <t>Продавец</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/155897954/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/565713653/detail.aspx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -808,33 +808,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>RTX 5080 GAMINGPRO OC 16 ГБ (NE75080S19T2-GB2031A)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>663131053</v>
+        <v>560729608</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MUNIRA</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MUNIRA collection</t>
+          <t>Продавец</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/663131053/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/560729608/detail.aspx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -846,33 +846,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Куртка демисезонная стеганая с поясом</t>
+          <t>Видеокарта RX 9060XT 16 ГБ RTL (90YV0LG2-M0NA00)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36304301</v>
+        <v>705837299</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VAMPONI</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VAMPONI</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/36304301/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/705837299/detail.aspx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -884,33 +884,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Куртка кожаная пиджак косуха</t>
+          <t>Видеокарта RTX 5060 Ti TWIN X2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>143610231</v>
+        <v>737258396</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KONVY</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KONVY</t>
+          <t>Chaban Base</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/143610231/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/737258396/detail.aspx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -922,33 +922,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз с капюшоном весна</t>
+          <t>Видеокарта для пк RTX 5080 16ГБ GDDR7 DLSS игровая</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>458514779</v>
+        <v>399733754</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>by LuLu</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>by LuLu</t>
+          <t>СИТИЛИНК</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/458514779/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/399733754/detail.aspx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -960,33 +960,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Весенняя куртка длинная</t>
+          <t>Видеокарта RX 9070XT 16 ГБ RTL (DP.Z4FWW.P01)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>97202282</v>
+        <v>676209794</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Acer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/97202282/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/676209794/detail.aspx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -998,33 +998,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Куртка стеганая демисезонная с капюшоном и поясом</t>
+          <t>RTX 5070 Ti WINDFORCE OC SFF 16 ГБ (GV-N507TWF3OC-16GD)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>431054122</v>
+        <v>560709672</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAROI</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LAROI</t>
+          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/431054122/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/560709672/detail.aspx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1036,33 +1036,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров с капюшоном</t>
+          <t>RTX 5070 Twin Edge 12 ГБ (ZT-B50700E-10P)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>171325115</v>
+        <v>578723918</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AvantaC</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HadMart</t>
+          <t>ООО "ПРОМ-ЭНЕРГО"</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/171325115/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/578723918/detail.aspx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1074,33 +1074,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Кожаная куртка для женщин демисезон с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5060 Ti 16GB TWIN X2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>341378733</v>
+        <v>725979824</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bless You Today</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bless You</t>
+          <t>PC City</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/341378733/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/725979824/detail.aspx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1112,33 +1112,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Куртка на осень короткая оверсайз</t>
+          <t>Видеокарта Geforce RTX 5060 Ti TWIN X2</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>314963479</v>
+        <v>611984887</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>POLAIR</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>POLAIR</t>
+          <t>Cyber shop</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/314963479/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/611984887/detail.aspx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1150,33 +1150,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Куртка с эко-норкой и капюшоном</t>
+          <t>Видеокарта ROG Astral GeForce RTX 5080 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>596709668</v>
+        <v>781957564</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ladyexclusive</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ladyexclusive</t>
+          <t>TDX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/596709668/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/781957564/detail.aspx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1188,33 +1188,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Куртка стеганая демисезонная женская</t>
+          <t>Видеокарта GeForce RTX 5080 16G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>314703133</v>
+        <v>323039306</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TIMAMI</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TIMAMI</t>
+          <t>Getsy</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/314703133/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/323039306/detail.aspx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1226,33 +1226,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Куртка женская весна с капюшоном</t>
+          <t>RX 9060 XT PURE OC 16 ГБ (11350-02-20G)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>207655137</v>
+        <v>564311113</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>iNeed</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>iNeed &amp; IRONSIDE</t>
+          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/207655137/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/564311113/detail.aspx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1264,33 +1264,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Демисезонная куртка с мехом утепленная</t>
+          <t>Видеокарта RTX 5060TI INFINITY 3 OC 16ГБ GDDR7 4608 ядер</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>182543456</v>
+        <v>687118968</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasonika</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BOGERA</t>
+          <t>СИТИЛИНК</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/182543456/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/687118968/detail.aspx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1302,33 +1302,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном</t>
+          <t>Видеокарта ROG Astral GeForce RTX 5080 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>506319884</v>
+        <v>781806874</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virton</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VIRTON</t>
+          <t>IT-D</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/506319884/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/781806874/detail.aspx</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1340,33 +1340,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Куртка с замшевой фактурой утепленная без капюшона</t>
+          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (ZT-B50620E-10M)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>733931399</v>
+        <v>526625042</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Befree</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/733931399/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/526625042/detail.aspx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1378,33 +1378,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Куртка-пуховик зимняя парка с мехом и капюшоном</t>
+          <t>RX 9070 XT NITRO+ OC 16 ГБ (11348-01-20G)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>256204207</v>
+        <v>823110282</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LUXINE</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Женская одежда LUXINE</t>
+          <t>Продавец</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/256204207/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/823110282/detail.aspx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1416,33 +1416,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная с капюшоном</t>
+          <t>RTX 5070 GamingPro-S 12 ГБ (NE75070019K9-GB2050U)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>699575812</v>
+        <v>560720133</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PULMOND</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PULMOND</t>
+          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/699575812/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/560720133/detail.aspx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1454,33 +1454,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Куртка кожаная женская большие размеры</t>
+          <t>Видеокарта RTX 5080 16 ГБ RTL (GV-N5080AERO OC-16GD)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>202323739</v>
+        <v>502308708</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Noelle sharm</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Noelle sharm</t>
+          <t>Gigabyte Official Store</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/202323739/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502308708/detail.aspx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1492,33 +1492,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Весенняя куртка короткая</t>
+          <t>Видеокарта RX 9070 XT GAMING OC 16G, 16 Гб GDDR6 UltraHD</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>436675245</v>
+        <v>445280948</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LOTS</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LOTS</t>
+          <t>Getsy</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/436675245/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/445280948/detail.aspx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1530,33 +1530,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка удлиненная с капюшоном</t>
+          <t>Видеокарта RX 9070 GAMING OC 16G, 16 Гб GDDR6</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>246763829</v>
+        <v>445318305</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SIIRA</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SIIRA</t>
+          <t>Omni Market</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/246763829/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/445318305/detail.aspx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1568,33 +1568,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Куртка демисезонная стеганая с капюшоном и поясом</t>
+          <t>Видеокарта GeForce RTX 5060 8G SHADOW 2X OC MAX</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>697127524</v>
+        <v>814743980</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BONOMI</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BONOMI</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/697127524/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/814743980/detail.aspx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1606,33 +1606,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Куртка женская демисезонная большие размеры осень</t>
+          <t>Видеокарта GeForce RTX 5070 Infinity 3 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>86497379</v>
+        <v>597161650</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kera</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Женская одежда Kera и детская одежда Пиколино</t>
+          <t>TDX</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/86497379/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/597161650/detail.aspx</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1644,33 +1644,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Куртка демисезонная укороченная утепленная</t>
+          <t>Видеокарта RTX 5070 WHITE OC 12GB PALIT</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>458311484</v>
+        <v>762389768</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bemansa</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bemansa</t>
+          <t>Надо брать!</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/458311484/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/762389768/detail.aspx</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1682,33 +1682,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Куртка демисезонная</t>
+          <t>Видеокарта RTX 5080 X3 OC</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>120163258</v>
+        <v>790818747</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ZAVATORIA</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ZAVATORIA</t>
+          <t>Lumono</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/120163258/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/790818747/detail.aspx</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1720,33 +1720,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Куртка с поясом демисезонная удлиненная</t>
+          <t>Видеокарта RTX 5080 16 ГБ RTL (GV-N5080AORUSM ICE-16GD)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>500314245</v>
+        <v>502308696</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vera Nicco</t>
+          <t>AORUS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vera Nicco</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/500314245/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502308696/detail.aspx</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1758,33 +1758,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Куртка экокожа косуха пиджак</t>
+          <t>RTX 5060 Ti Battle AX DUO 16 ГБ (RTX 5060 Ti Battle AX DUO 16GB-V)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>200620484</v>
+        <v>729250187</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AM&amp;PA</t>
+          <t>Colorful</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AM&amp;PA</t>
+          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/200620484/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/729250187/detail.aspx</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1796,33 +1796,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая с капюшоном</t>
+          <t>Видеокарта ASUS GeForce RTX 5070 12 ГБ GDDR7 Prime</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>712835789</v>
+        <v>723151906</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MSstyle</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MSstyle</t>
+          <t>BestRAM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/712835789/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/723151906/detail.aspx</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1834,33 +1834,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Игровая видеокарта AMD Radeon RX 580 8Gb GDDR5 RX580 8 Гб</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>473034287</v>
+        <v>164656358</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lofajoy</t>
+          <t>JieShuo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LOFAJOY</t>
+          <t>COSMO-V</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473034287/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/164656358/detail.aspx</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1872,33 +1872,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном оверсайз</t>
+          <t>Видеокарта AMD Radeon RX 9070 Challenger 16GB</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>768371423</v>
+        <v>817479717</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eberron</t>
+          <t>ASRock</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eberron</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/768371423/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/817479717/detail.aspx</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1910,33 +1910,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Куртка тонкая демисезонная с капюшоном</t>
+          <t>RTX 5060 iCraft AIGA OC 8 ГБ (MS-RTX5060 iCraft OC8G AIGA)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>807017929</v>
+        <v>766403735</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sofiny</t>
+          <t>Maxsun</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SOFINY</t>
+          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/807017929/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/766403735/detail.aspx</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1948,33 +1948,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная с капюшоном</t>
+          <t>PELADN GeForce RTX 3060 Ti 8GB ARMOUR</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>338330063</v>
+        <v>689196268</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BYSHU</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BYSHU</t>
+          <t>To gamers from a gamer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/338330063/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/689196268/detail.aspx</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1986,33 +1986,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Куртка женская демисезон с капюшоном натуральный мех</t>
+          <t>Видеокарта Asus E3504U-C DUAL- GEFORCE RTX5060-8G</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>142254839</v>
+        <v>704884457</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RUTE</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ПЕРЕЙТИ В КАТАЛОГ</t>
+          <t>Techno Bisal</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/142254839/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/704884457/detail.aspx</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2024,33 +2024,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Видеокарта 5060 VENTUS 3X OC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>355829416</v>
+        <v>738949384</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SONAME STUDIO</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SONAME studio</t>
+          <t>Яратон</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/355829416/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/738949384/detail.aspx</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2062,33 +2062,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Куртка длинная зимняя с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5070 Ti SHADOW 3X OC, 16 ГБ</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>100911533</v>
+        <v>482977120</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GAINRUSANOV</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GAINRUSANOV</t>
+          <t>240km/h Market</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/100911533/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/482977120/detail.aspx</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2100,33 +2100,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Куртка весенняя парка с капюшоном удлиненная</t>
+          <t>Видеокарта RX 9060XT 16 ГБ RTL (11350-03-20G)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>795165595</v>
+        <v>757417447</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>By BUtton</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>By BUtton</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/795165595/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/757417447/detail.aspx</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2138,33 +2138,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Весенняя куртка стеганая</t>
+          <t>Видеокарта GeForce RTX 5060 Dual Fan</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>533380570</v>
+        <v>668899409</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LawBeauty</t>
+          <t>PNY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MARMAT</t>
+          <t>Железный Король</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/533380570/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/668899409/detail.aspx</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2176,33 +2176,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Стеганая куртка демисезонная с капюшоном</t>
+          <t>Видеокарта Intel Arc B580 iCraft 12G</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>305979107</v>
+        <v>531846287</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tyne</t>
+          <t>Maxsun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tyne</t>
+          <t>Magdevice</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/305979107/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/531846287/detail.aspx</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2214,33 +2214,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Двусторонняя весенняя фуфайка куртка стеганная женская</t>
+          <t>GeForce GTX 1660 SUPER VENTUS XS OC 6GB Игровая</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>314241736</v>
+        <v>156549910</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nurbelek</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>МУСУРАЛИЕВА Д.Н.</t>
+          <t>To gamers from a gamer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/314241736/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/156549910/detail.aspx</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2252,33 +2252,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном весенняя большие размеры</t>
+          <t>Видеокарта GEFORCE RTX 5070 12GB OC</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>772423972</v>
+        <v>850804121</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Acalypha</t>
+          <t>PNY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Acalypha</t>
+          <t>Хайтек Плюс</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/772423972/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/850804121/detail.aspx</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2290,33 +2290,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Куртка демисезонная кимоно пиджак</t>
+          <t>Видеокарта RX 9070 XT OC 16GB GDDR6 ASUS TUF Gaming Radeon</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>719653546</v>
+        <v>832353082</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zunelle</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zunelle</t>
+          <t>FUJILAB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/719653546/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/832353082/detail.aspx</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2328,33 +2328,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная оверсайз с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5070 12 ГБ (NE75070019K9-GB2050U)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>721247735</v>
+        <v>760667535</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Positive Mind</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HONEY GLOW</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/721247735/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/760667535/detail.aspx</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2366,33 +2366,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Куртка демисезонная на запах с поясом</t>
+          <t>Видеокарта AMD Radeon RX 9070 XT Prime OC White 16 ГБ</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>332614606</v>
+        <v>571277020</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SHATILOVA M.V.</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SHATILOVA</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/332614606/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/571277020/detail.aspx</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2404,33 +2404,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Кожаная куртка на кулиске оверсайз</t>
+          <t>Видеокарта Radeon RX9070 XT OC 16Gb TUF-RX9070XT-O16G-GAMING</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>460447909</v>
+        <v>543916044</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BLUMONE</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BLUMONE</t>
+          <t>ХОЛОДИЛЬНИК.ру</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460447909/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/543916044/detail.aspx</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2442,33 +2442,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном стеганая</t>
+          <t>Видеокарта RTX 5070 12G DUAL OC, 12 ГБ GDDR7 UltraHD</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>504904986</v>
+        <v>451820702</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RUMOUR</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ромашка</t>
+          <t>Getsy</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/504904986/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/451820702/detail.aspx</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2480,33 +2480,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Куртка весенняя бомбер с капюшоном утепленный</t>
+          <t>Видеокарта NVIDIA GeForce RTX 5060 Shadow 2X OC</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>316934243</v>
+        <v>538357893</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ELZAZ</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NSWEAR</t>
+          <t>Hard Comp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/316934243/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/538357893/detail.aspx</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2518,33 +2518,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Джинсовая куртка удлиненная стрейч</t>
+          <t>Видеокарта игровая для пк TUF Gaming GeForce RTX 5070 12GB</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>200735882</v>
+        <v>618427434</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>EKATERINA FEDRES - производитель с 2001г.</t>
+          <t>ЕСЦ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/200735882/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/618427434/detail.aspx</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2556,33 +2556,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Видеокарта MSI RTX 5060 Ti 8G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>795221669</v>
+        <v>608357604</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>YOUONE</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ВЗВ</t>
+          <t>AWSD</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/795221669/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/608357604/detail.aspx</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2594,33 +2594,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с поясом и капюшоном удлиненная</t>
+          <t>Видеокарта GeForce RTX 5080 GamingPro</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>172283339</v>
+        <v>815251970</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JULI PITON</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JULI PITON</t>
+          <t>МультиБренд</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/172283339/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/815251970/detail.aspx</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2632,33 +2632,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Куртка демисезонная весна парка с капюшоном</t>
+          <t>Видеокарта RX 9070 16GB GV-R9070GAMING OC-16GD</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>316610837</v>
+        <v>542394046</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jenny Poletty</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jenny Poletty</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/316610837/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/542394046/detail.aspx</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2670,33 +2670,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная стройнит</t>
+          <t>GeForce GTX 1660 SUPER 6GB GDDR6</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>172231945</v>
+        <v>538270698</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lisa Bella</t>
+          <t>PelaDN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LisaBella</t>
+          <t>IKARD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/172231945/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/538270698/detail.aspx</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2708,33 +2708,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном весна</t>
+          <t>Видеокарта NVIDIA GeForce RTX 5060 Infinity 3 OC 8 ГБ</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>316275211</v>
+        <v>758526174</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MOOX</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>МООХ</t>
+          <t>ElectroTron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/316275211/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/758526174/detail.aspx</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2746,33 +2746,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном</t>
+          <t>Видеокарта PCI-E 4.0 RTX3050-O6G-LP-BRK NV RTX3050 6Gb 96bit</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>467762621</v>
+        <v>377359826</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leoni Aoki</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leoni Aoki</t>
+          <t>СИТИЛИНК</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/467762621/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/377359826/detail.aspx</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2784,33 +2784,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>63</v>
+        <v>231</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров с капюшоном</t>
+          <t>Видеокарта 5080 ARGB EPIC-X RGB OC Triple Fan GPU</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>720961971</v>
+        <v>656934759</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>La Zelia</t>
+          <t>PNY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>La Zelia</t>
+          <t>Cyber shop</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/720961971/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/656934759/detail.aspx</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2822,33 +2822,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая стеганая ветровка с капюшоном</t>
+          <t>Видеокарта для ПК Radeon RX 5500 XT 8 гб GDDR6 игровая новая</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>146354941</v>
+        <v>835633478</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MulluMix</t>
+          <t>PelaDN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MulluMix Fashion</t>
+          <t>ViaBit</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/146354941/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/835633478/detail.aspx</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2860,33 +2860,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Куртка короткая</t>
+          <t>Видеокарта GeForce GTX 750 Ti 4GB</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>198656127</v>
+        <v>495629076</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clozer</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clozer</t>
+          <t>RedGoosePC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/198656127/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/495629076/detail.aspx</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2898,33 +2898,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Куртка оверсайз демисезонная утепленная с капюшоном</t>
+          <t>NVIDIA GeForce RTX 3070 Ti 8GB GDDR6 AMOUR</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>306170378</v>
+        <v>694269149</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SELFIE SHOP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SELFIE SHOP &amp; BROKSTONE</t>
+          <t>To gamers from a gamer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/306170378/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/694269149/detail.aspx</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2936,33 +2936,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая с капюшоном оверсайз</t>
+          <t>Видеокарта GeForce RTX 5060 Ti 16 GB Infinity 3 OC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>462993870</v>
+        <v>839564791</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unigou</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UNIGOU</t>
+          <t>Marlen</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/462993870/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/839564791/detail.aspx</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2974,33 +2974,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>68</v>
+        <v>271</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Удлиненная стеганая куртка</t>
+          <t>Видеокарта GeForce RTX 5060 Ti Infinity 3 16GB GDDR7</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>330934054</v>
+        <v>758185742</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FROGMAN</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Butique</t>
+          <t>IT-D</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/330934054/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/758185742/detail.aspx</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3012,33 +3012,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>69</v>
+        <v>272</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка удлиненная с капюшоном</t>
+          <t>Видеокарта RTX5050 8GB RTX 5050 8G SHADOW 2X OC MSI</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>699884583</v>
+        <v>762759860</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VERLENTA</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ИП Шумакова</t>
+          <t>Надо брать!</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/699884583/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/762759860/detail.aspx</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3050,33 +3050,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>70</v>
+        <v>285</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Куртка кожаная с мехом демисезонная утепленная</t>
+          <t>Видеокарта GeForce RTX 5060 WINDFORCE OC 8G</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>765127124</v>
+        <v>633482563</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fali</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fali</t>
+          <t>Яратон</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/765127124/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/633482563/detail.aspx</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3088,33 +3088,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Пиджак стеганый куртка жакет фуфайка</t>
+          <t>Видеокарта RTX 5060 Dual OC</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>355086944</v>
+        <v>788498445</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MokoLo</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MokoLo</t>
+          <t>Lumono</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/355086944/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/788498445/detail.aspx</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3126,33 +3126,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>72</v>
+        <v>289</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Куртка кожаная короткая стеганая</t>
+          <t>Видеокарта GEFORCE RTX 5070 12GB OC</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>174093208</v>
+        <v>814985975</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>PNY</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>МультиБренд</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/174093208/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/814985975/detail.aspx</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3164,33 +3164,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>73</v>
+        <v>290</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Весенняя куртка демисезонная больших размеров</t>
+          <t>Видеокарта GeForce RTX 5060 8GB Infinity 2 OC</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>732466710</v>
+        <v>850804026</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ELMARI</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ELMARI</t>
+          <t>Хайтек Плюс</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/732466710/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/850804026/detail.aspx</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3202,33 +3202,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Куртка зимняя с капюшоном удлиненная</t>
+          <t>Видеокарта PALIT RTX5060 INFINITY 2 OC 8GB</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>246127195</v>
+        <v>742580902</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NiceJune</t>
+          <t>Gigabyte GeForce</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NJ TOP</t>
+          <t>Telenova</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/246127195/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/742580902/detail.aspx</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3240,33 +3240,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Джинсовая куртка с капюшоном</t>
+          <t>Игровая видеокарта JieShuo RX 580 8gb</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>217682337</v>
+        <v>649742483</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cersi</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cersi</t>
+          <t>PELADN Official Store</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/217682337/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/649742483/detail.aspx</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3278,33 +3278,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>76</v>
+        <v>339</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Куртка бомбер с капюшоном демисезонная</t>
+          <t>Radeon RX 6600 XT 8GB GDDR6 (rx6600xt)</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>250110394</v>
+        <v>310585167</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UMO SHOP</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UMO</t>
+          <t>ElectroRon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/250110394/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/310585167/detail.aspx</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3316,33 +3316,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз стеганая легкая пуховая</t>
+          <t>Видеокарта GeForce RTX 5060 Ti Windforce 16GB GDDR7</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>692819565</v>
+        <v>776182946</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BULMER</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bulmer</t>
+          <t>TDX</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/692819565/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/776182946/detail.aspx</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3354,33 +3354,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5060 WHITE OC</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>756244179</v>
+        <v>837573178</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OffCold</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Комфорт</t>
+          <t>Яратон</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/756244179/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/837573178/detail.aspx</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3392,33 +3392,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
+          <t>Radeon RX 5500XT 8GD 8ГБ GDDR6 (RX5500XT) игровая BLACK-RED</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>760835247</v>
+        <v>195487503</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mare Blanco</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maré Blanco</t>
+          <t>To gamers from a gamer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/760835247/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/195487503/detail.aspx</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3430,33 +3430,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном короткая</t>
+          <t>Видеокарта для пк игровая GeForce RTX 5070TI Eagle 16Gb</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>251610433</v>
+        <v>584504104</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MARUZE</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MaruZE</t>
+          <t>ЭлМир</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/251610433/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/584504104/detail.aspx</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3468,33 +3468,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Куртка зимняя с капюшоном оверсайз</t>
+          <t>Видеокарта Graphiccard R7-350 (PCI-E 3.0 2 GB GDDR5)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>268947499</v>
+        <v>542565225</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ALAINIX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ALAINIX</t>
+          <t>YOffice</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/268947499/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/542565225/detail.aspx</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3506,33 +3506,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
+          <t>Видеокарта RTX 3060 12 ГБ RTL (AF3060-12GD6H7-V4)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>678700723</v>
+        <v>757417679</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GLAUREN</t>
+          <t>AFOX</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>GLAUREN</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/678700723/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/757417679/detail.aspx</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3544,33 +3544,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз</t>
+          <t>Видеокарта RX580 8GB (RX 580 8ГБ) 2048SP</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>721141997</v>
+        <v>560755558</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ROCK-LAB</t>
+          <t>XFX</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ROCK-LAB</t>
+          <t>To gamers from a gamer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/721141997/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/560755558/detail.aspx</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3582,33 +3582,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном</t>
+          <t>Видеокарта игровая PALIT Geforce rtx 3070 8gb</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>753224837</v>
+        <v>786203236</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>WINDYCOATS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Одежда и товары для комфортной жизни</t>
+          <t>PELADN Official Store</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/753224837/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/786203236/detail.aspx</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3620,33 +3620,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном оверсайз</t>
+          <t>Видеокарта Radeon RX7600 OC</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>728859616</v>
+        <v>787435795</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>My Gelato</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Malachite</t>
+          <t>Lumono</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/728859616/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/787435795/detail.aspx</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3658,33 +3658,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>86</v>
+        <v>377</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Куртка весенняя кимоно с поясом</t>
+          <t>RTX 5070 DUAL OC 12 ГБ (DUAL-RTX5070-O12G)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>336912945</v>
+        <v>869172900</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MILLYS</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MILLYS</t>
+          <t>Мерлион</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/336912945/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/869172900/detail.aspx</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3696,33 +3696,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>87</v>
+        <v>381</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном удлиненная на кулиске</t>
+          <t>Видеокарта RTX 2060 6 ГБ RTL (NK206FG66F)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>744166513</v>
+        <v>781067134</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ZEKKA</t>
+          <t>Ninja (Sinotex)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zekka</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/744166513/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/781067134/detail.aspx</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3734,33 +3734,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>88</v>
+        <v>394</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Куртка весенняя удлиненная больших размеров с капюшоном</t>
+          <t>Видеокарта Dual GeForce RTX 5060 OC</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>758272149</v>
+        <v>600970110</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DORELIA</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ALKONDA</t>
+          <t>Fly Buy</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/758272149/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/600970110/detail.aspx</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3772,33 +3772,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>89</v>
+        <v>398</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Куртка ветровка с поясом и капюшоном демисезонная легкая</t>
+          <t>Видеокарта GeForce RTX 5070 Twin X2</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>148954022</v>
+        <v>772866212</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vlasova</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ИП Огнев</t>
+          <t>Яратон</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/148954022/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/772866212/detail.aspx</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3810,33 +3810,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Куртка женская демисезонная</t>
+          <t>Видеокарта RTX 3070 8ГБ (NF307FG86F)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>262218128</v>
+        <v>173461586</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rosabella</t>
+          <t>SINOTEX</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/262218128/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/173461586/detail.aspx</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3848,33 +3848,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>91</v>
+        <v>406</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая</t>
+          <t>Видеокарта GeForce RTX 5060 GAMING Twin Edge OC</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>732991342</v>
+        <v>841454452</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MONAPURE</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MONAPURE</t>
+          <t>Яратон</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/732991342/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/841454452/detail.aspx</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3886,33 +3886,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>92</v>
+        <v>412</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном больших размеров</t>
+          <t>Видеокарта Gunnir Arc A580 Index 8 ГБ GDDR6 HDMI</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>174113381</v>
+        <v>593694089</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Freedom shop</t>
+          <t>GUNNIR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Freedom shop</t>
+          <t>Скорость ПК</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/174113381/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/593694089/detail.aspx</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3924,33 +3924,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>93</v>
+        <v>423</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Куртка на кулиске весенняя</t>
+          <t>Видеокарта GeForce RTX 3070 Gaming 8Gb</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>502648560</v>
+        <v>762675367</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MOLLO</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nurova</t>
+          <t>Чип Дейли</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/502648560/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/762675367/detail.aspx</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3962,33 +3962,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>94</v>
+        <v>424</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров</t>
+          <t>Видеокарта WINDFORCE MAX OC 8Gb GEFORCE RTX 5060</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>25846173</v>
+        <v>764884571</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STYLE MC CLASSIC</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>STYLE MC CLASSIC</t>
+          <t>Techno Bisal</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/25846173/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/764884571/detail.aspx</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4000,33 +4000,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>95</v>
+        <v>429</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Куртка демисезонная укороченная утепленная с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5070 Python III</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>247644567</v>
+        <v>804283800</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Miletti</t>
+          <t>Gainward</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>DeaMILETTI</t>
+          <t>Diplay</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/247644567/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/804283800/detail.aspx</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4038,33 +4038,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>96</v>
+        <v>433</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном короткая</t>
+          <t>Мощная игровая видеокарта для компьютера ASUS RX 580 8GB</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>734218253</v>
+        <v>768067518</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SEREBRYX</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Кальмиус</t>
+          <t>PELADN Official Store</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/734218253/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/768067518/detail.aspx</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4076,33 +4076,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>97</v>
+        <v>440</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном утепленная</t>
+          <t>Игровая видеокарта NVIDIA GeForce GTX 1060 DUAL 6G белая</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>460270627</v>
+        <v>415291929</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MERAQVIN</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>АН</t>
+          <t>Компьютерная техника РФ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460270627/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/415291929/detail.aspx</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4114,33 +4114,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>98</v>
+        <v>441</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров</t>
+          <t>Видеокарта GeForce RTX 5060 Ti Eagle Max OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>209651656</v>
+        <v>583695370</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PUVILDRA</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Be in fashion</t>
+          <t>IT-D</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/209651656/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/583695370/detail.aspx</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4152,33 +4152,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>99</v>
+        <v>442</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Куртка пиджак весенняя стежка с поясом черная</t>
+          <t>RTX 5060 Ti INFINITY 3 16 ГБ (NE7506T019T1-GB2061S)</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>204535569</v>
+        <v>869172843</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reprise</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Женская одежда</t>
+          <t>Мерлион</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/204535569/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/869172843/detail.aspx</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4190,33 +4190,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>100</v>
+        <v>463</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном</t>
+          <t>Игровая видеокарта для пк GeForce GT 730 4GB</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>734083997</v>
+        <v>471058531</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lofel</t>
+          <t>Atermiter</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>LOFEL</t>
+          <t>Acs Quality</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/734083997/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/471058531/detail.aspx</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4228,33 +4228,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>101</v>
+        <v>469</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном стеганая</t>
+          <t>Видеокарта RTX 5060 AERO OC 8GB (GV-N5060AERO OC-8GD)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>387424622</v>
+        <v>501135388</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>EL'MAGIC</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ЭЛЬ'МЭЙДЖИК / EL'MAGIC</t>
+          <t>ХОЛОДИЛЬНИК.ру</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/387424622/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/501135388/detail.aspx</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4266,33 +4266,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>102</v>
+        <v>473</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Куртка бомбер кожаная оверсайз</t>
+          <t>Видеокарта GeForce GTX 1050 TI 4 ГБ</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>492564098</v>
+        <v>477997053</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Moroz Brand</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Moroz brand</t>
+          <t>GameWork</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/492564098/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/477997053/detail.aspx</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4304,33 +4304,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>103</v>
+        <v>474</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Куртка весенняя с рукавом реглан</t>
+          <t>Видеокарта GeForce RTX 5080 WINDFORCE OC SFF 16G</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>343281349</v>
+        <v>822706561</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Binitra Bini</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Binitra Bini</t>
+          <t>Салонсвязи.ру</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/343281349/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/822706561/detail.aspx</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4342,33 +4342,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>104</v>
+        <v>483</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Куртка бомбер демисезонная</t>
+          <t>RTX 5070 INSPIRE 3X OC 12 ГБ (RTX 5070 12G INSPIRE 3X OC)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>710194493</v>
+        <v>869172845</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ТВОЕ</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ТВОЕ</t>
+          <t>Мерлион</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/710194493/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/869172845/detail.aspx</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4380,33 +4380,33 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>105</v>
+        <v>493</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Куртка стеганая больших размеров демисезонная</t>
+          <t>Видеокарта ASUS GeForce RTX 5060 Dual OC Edition</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>102576166</v>
+        <v>518253901</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ASTEXVEL</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ASTEXVEL</t>
+          <t>TOO 1WN TRADE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/102576166/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/518253901/detail.aspx</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4418,33 +4418,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>106</v>
+        <v>510</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая</t>
+          <t>Видеокарта Sapphire PCI-E 4.0 11314-07-20G RX 6500XT Gaming</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>247455605</v>
+        <v>541496803</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ANOLTA</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>А.С</t>
+          <t>СИТИЛИНК</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/247455605/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/541496803/detail.aspx</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4456,33 +4456,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>107</v>
+        <v>516</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров с капюшоном</t>
+          <t>Игровая Видеокарта для ПК NVIDIA GeForce GTX 1050 Ti OC 4G</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>317820717</v>
+        <v>435632786</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Luxury Plus</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luxury Plus</t>
+          <t>Компьютерная техника РФ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/317820717/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/435632786/detail.aspx</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4494,33 +4494,33 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>108</v>
+        <v>517</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Куртка на пуху демисезонная</t>
+          <t>Видеокарта для ПК NVIDIA GeForce GTX 1050 Ti с Подсветкой</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>496472475</v>
+        <v>415277124</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>fameForce</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FameForce</t>
+          <t>Компьютерная техника РФ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/496472475/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/415277124/detail.aspx</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4532,33 +4532,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>109</v>
+        <v>518</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном больших размеров</t>
+          <t>Видеокарта GeForce RTX 5070 GAMING TRIO OC, 12 ГБ GDDR7, 8K</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>327487633</v>
+        <v>445266087</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Милледи</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Милледи</t>
+          <t>Omni Market</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/327487633/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/445266087/detail.aspx</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4570,33 +4570,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>110</v>
+        <v>520</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Удлиненная куртка парка демисезонная с капюшоном</t>
+          <t>Видеокарта игровая RTX 5070 GamingPro-S 12ГБ GDDR7</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>753846707</v>
+        <v>449793252</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RAMORE</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RAMORE</t>
+          <t>Позитроника</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/753846707/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/449793252/detail.aspx</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4608,33 +4608,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>111</v>
+        <v>531</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Куртка короткая с капюшоном демисезонная</t>
+          <t>Видеокарта GeForce RTX 5070 SOLID</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>169746779</v>
+        <v>725753242</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HOLODILOV</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ИП Холодилова А.С.</t>
+          <t>RAGATSHOP</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/169746779/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/725753242/detail.aspx</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4646,33 +4646,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Куртка больших размеров кожаная тренч</t>
+          <t>Видеокарта GeForce RTX 5070 Dual OC</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>206104869</v>
+        <v>736017853</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sharming Style</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sharming Style</t>
+          <t>Железный Король</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/206104869/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/736017853/detail.aspx</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4684,33 +4684,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>113</v>
+        <v>540</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном больших размеров</t>
+          <t>Видеокарта Asrock RX 5500 XT Challenger D OC 8Гб GDDR6</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>495869567</v>
+        <v>214439465</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gratia</t>
+          <t>ASRock</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Moodgirls</t>
+          <t>Laztorg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/495869567/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/214439465/detail.aspx</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4722,33 +4722,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>114</v>
+        <v>556</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Стеганая куртка демисезонная удлиненная</t>
+          <t>Видеокарта для ПК NVIDIA GeForce GTX1050Ti StormX 4G</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>455499423</v>
+        <v>435208093</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>DEES</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Магазин</t>
+          <t>Компьютерная техника РФ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/455499423/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/435208093/detail.aspx</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4760,33 +4760,33 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>115</v>
+        <v>558</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Игровая видеокарта Colorful GTX 1660 Super Battle-Ax</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>453526855</v>
+        <v>753842221</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Colorful</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SV Fashion</t>
+          <t>DELISE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/453526855/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/753842221/detail.aspx</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4798,33 +4798,33 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>116</v>
+        <v>564</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Джинсовка бомбер с капюшоном оверсайз</t>
+          <t>Видеокарта Radeon RX 5700 XT 8GB GDDR6 (rx5700xt)8гб игровая</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>340633288</v>
+        <v>434638230</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LEONALOVE</t>
+          <t>JieShuo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LEONALOVE</t>
+          <t>REMHATEK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/340633288/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/434638230/detail.aspx</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4836,33 +4836,33 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>117</v>
+        <v>565</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном удлиненная</t>
+          <t>Видеокарта Radeon RX 5500 8GB GDDR6 (rx5500 8gb)</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>744318538</v>
+        <v>447965373</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SALVIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Salvia</t>
+          <t>REMHATEK</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/744318538/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/447965373/detail.aspx</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4874,33 +4874,33 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>118</v>
+        <v>572</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Куртка больших размеров весенняя</t>
+          <t>Видеокарта AMD Radeon 9070 Challenger</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>441463601</v>
+        <v>927404155</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ASRock</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AiSofia</t>
+          <t>Бутик спорта</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/441463601/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/927404155/detail.aspx</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4912,33 +4912,33 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>119</v>
+        <v>573</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном на весну</t>
+          <t>Видеокарта RTX 5090 GAMING TRIO OC</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>530958151</v>
+        <v>927401883</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SAMULIN</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SAMULIN</t>
+          <t>Бутик спорта</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/530958151/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/927401883/detail.aspx</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4950,33 +4950,33 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>120</v>
+        <v>575</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном парка</t>
+          <t>Видеокарта Palit GeForce RTX 5080 GamingPro</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>753396582</v>
+        <v>907354129</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MOMNALI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>E.N.V. Brand</t>
+          <t>ПРОФСВЯЗЬ-РО</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/753396582/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/907354129/detail.aspx</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4988,33 +4988,33 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>121</v>
+        <v>576</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Тёплая женская куртка с воротником</t>
+          <t>Видеокарта Prime GeForce RTX 5070 Ti 16 ГБ GDDR7 OC</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>758116829</v>
+        <v>881370678</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zolla</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zolla</t>
+          <t>BestRAM</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/758116829/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/881370678/detail.aspx</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5026,33 +5026,33 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>122</v>
+        <v>584</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном удлиненная</t>
+          <t>RTX 5070 Ti EAGLE OC ICE SFF 16 ГБ (GV-N507TEAGLEOC ICE-16GD…</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>456472357</v>
+        <v>869172860</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>MONOMIR</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MONOMIR</t>
+          <t>Мерлион</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456472357/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/869172860/detail.aspx</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5064,33 +5064,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>123</v>
+        <v>594</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз</t>
+          <t>Видеокарта GeForce RTX 3050 StormX 6ГБ</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>597021892</v>
+        <v>867286101</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LuMini Style</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LuMini</t>
+          <t>Digital.zone</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/597021892/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/867286101/detail.aspx</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5102,33 +5102,33 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>124</v>
+        <v>596</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Куртка демисезонная короткая</t>
+          <t>GeForce RTX 5070 Infinity 3 OC [NE75070S19K9-GB2050S]</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>763730369</v>
+        <v>853333396</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trend product</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Все товары</t>
+          <t>Finest Gadgets</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/763730369/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/853333396/detail.aspx</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5140,33 +5140,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>125</v>
+        <v>606</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Куртка рабочего женская тренд</t>
+          <t>Видеокарта GEFORCE RTX 5070 INFINITY 3 12 GB GDDR7</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>471096415</v>
+        <v>828887045</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Verh</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Verh</t>
+          <t>Techno Bisal</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/471096415/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/828887045/detail.aspx</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5178,33 +5178,33 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>126</v>
+        <v>618</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Куртка весенняя короткая стеганая с мехом</t>
+          <t>Видеокарта RTX 5060 Ti 8G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>173306811</v>
+        <v>820619229</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ezewika</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ezewika</t>
+          <t>Салонсвязи.ру</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/173306811/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/820619229/detail.aspx</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5216,33 +5216,33 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>127</v>
+        <v>625</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном и поясом</t>
+          <t>Видеокарта PCI-E GIGABYTE P104-100 MINING 8192MB GDDR5Х 8ГБ</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>248266222</v>
+        <v>820347294</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ZHENECHKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Женечка</t>
+          <t>ЮЛИКС</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/248266222/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/820347294/detail.aspx</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5254,33 +5254,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>128</v>
+        <v>628</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Куртка пуховик с капюшоном зимний</t>
+          <t>Видеокарта GTX 1660 SUPER (GV-N166SD6-6GD) 6Гб GDDR6</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>443658277</v>
+        <v>815890622</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Modjimoda</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Modjimoda</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/443658277/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/815890622/detail.aspx</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5292,33 +5292,33 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>129</v>
+        <v>631</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Куртка стеганая удлиненная осень с капюшоном</t>
+          <t>Видеокарта ASUS Radeon RX 9070 XT TUF GAMING OC</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>174898626</v>
+        <v>815341363</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Мисс Данин</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Мисс Данин</t>
+          <t>Mirage</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/174898626/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/815341363/detail.aspx</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5330,33 +5330,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>130</v>
+        <v>634</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Куртка весенняя стёганая с капюшоном</t>
+          <t>AMD Radeon 9060 XT GAMING OC</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>727681195</v>
+        <v>809327694</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LuBvi.brand</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LubVi.brand(ЛюбВи.бренд)</t>
+          <t>Mirage</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/727681195/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/809327694/detail.aspx</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5368,33 +5368,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>131</v>
+        <v>636</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Куртка весенняя парка удлиненная оверсайз</t>
+          <t>Видеокарта RTX5060 Dual OC 8 ГБ (NE75060S19P1-GB2063D)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>719947363</v>
+        <v>807462489</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sweet Season</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CELEBRATE</t>
+          <t>ХОБОТ ДОСТАВИТ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/719947363/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/807462489/detail.aspx</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5406,33 +5406,33 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>132</v>
+        <v>637</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров</t>
+          <t>ONIX LUMI Arc B580 GDDR6 OC 12GB</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>490170063</v>
+        <v>795751124</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>EAST OCEAN</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>EAST OCEAN</t>
+          <t>TechBridgeUSA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/490170063/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/795751124/detail.aspx</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5444,33 +5444,33 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>133</v>
+        <v>638</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Куртка бомбер кожаный оверсайз</t>
+          <t>Видеокарта 12 Гб iGame GeForce RTX 3080 TI LHR Advanced OC-V</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>326905930</v>
+        <v>793419578</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>BASIC LINE</t>
+          <t>Colorful</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BASIC LINE</t>
+          <t>ZET-SHOP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/326905930/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/793419578/detail.aspx</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5482,33 +5482,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>134</v>
+        <v>642</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Рубашка джинсовая оверсайз</t>
+          <t>Видеокарта Radeon RX 9060 XT 8 GB GDDR6 (DP.Z4UWW.P02)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>235623846</v>
+        <v>783836186</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Feimailis</t>
+          <t>Acer</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>МС Джинс</t>
+          <t>Buyon</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/235623846/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/783836186/detail.aspx</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5520,33 +5520,33 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>135</v>
+        <v>661</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Куртка рабочего оверсайз под замшу на кулиске</t>
+          <t>Игровая видеокарта для пк rx 580 4GB GDDR5</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>481852936</v>
+        <v>774593050</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>MODERATOR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MD официальный магазин</t>
+          <t>santafe</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/481852936/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/774593050/detail.aspx</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5558,33 +5558,33 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>136</v>
+        <v>665</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Куртка теплая оверсайз демисезонная</t>
+          <t>Видеокарта AMD Radeon RX 9070 XT Predator Bifrost OC 16 ГБ</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>137342117</v>
+        <v>770954968</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ТЫСЯЧА СТОЛИЦ</t>
+          <t>Acer</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ТЫСЯЧА СТОЛИЦ</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/137342117/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770954968/detail.aspx</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5596,33 +5596,33 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>137</v>
+        <v>666</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном</t>
+          <t>Видеокарта GIGABYTE GAMING GeForce RTX 5060 Ti 16 ГБ</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>807800136</v>
+        <v>770587869</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>DORIMODES</t>
+          <t>BestRAM</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/807800136/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770587869/detail.aspx</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5634,33 +5634,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>138</v>
+        <v>667</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном ультралегкая</t>
+          <t>Видеокарта GeForce RTX 4070 WINDFORCE 2X OC V2</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>495664343</v>
+        <v>767199140</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PROSimple ПРОСимпл</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Мой Мир</t>
+          <t>ElectroHome</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/495664343/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/767199140/detail.aspx</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5672,33 +5672,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>139</v>
+        <v>687</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
+          <t>Видеокарта Zotac RTX 5070Ti Solid Sff 16Gb</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>689575236</v>
+        <v>762099961</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>GLDELUXE</t>
+          <t>ZOTAC GAMING</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GLDELUXE</t>
+          <t>ЭЛЕКТРОНИКА</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/689575236/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/762099961/detail.aspx</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5710,33 +5710,33 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>140</v>
+        <v>688</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном больших размеров</t>
+          <t>Видеокарта RTX 5060 SHADOW 2X OC 8 ГБ</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>466639026</v>
+        <v>761096262</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lady S+</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MP.seller</t>
+          <t>RG Electro</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/466639026/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/761096262/detail.aspx</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5748,33 +5748,33 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>141</v>
+        <v>704</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Куртка весенняя короткая стеганая большой размер</t>
+          <t>RTX 5060 Ti INFINITY 3 OC 16 ГБ (NE7506TS19T1-GB2061S)</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>169645664</v>
+        <v>756488716</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Moonmart</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Right Choice</t>
+          <t>Digital Land</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/169645664/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/756488716/detail.aspx</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5786,33 +5786,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>142</v>
+        <v>709</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном весна</t>
+          <t>Видеокарта RTX 5060 TWIN X2</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>825025741</v>
+        <v>740376129</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>DIONCE</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>DIONCE</t>
+          <t>Tech Store</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/825025741/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/740376129/detail.aspx</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5824,33 +5824,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>143</v>
+        <v>718</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном удлиненная еврозима</t>
+          <t>Видеокарта RTX 5070 Ti WINDFORCE OC SFF 16 ГБ, RTL</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>214070993</v>
+        <v>726188990</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ALPEX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ALPEX</t>
+          <t>Прекрасная Техника</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/214070993/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/726188990/detail.aspx</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5862,33 +5862,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>144</v>
+        <v>722</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Куртка - парка демисезонная с капюшоном</t>
+          <t>Видеокарта RTX 5080 WINDFORCE SFF 16 ГБ (GV-N5080WF3-16GD)</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>453891026</v>
+        <v>716330537</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Snow Belle</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SVOYAESTHETICA</t>
+          <t>NeoRim</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/453891026/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/716330537/detail.aspx</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5900,33 +5900,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>145</v>
+        <v>726</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Куртка Полиция МВД</t>
+          <t>RX 9060 XT PULSE GAMING OC 8GB (11350-04-20G)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>209873106</v>
+        <v>712754008</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>мвдформа</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>МВД ФОРМА</t>
+          <t>Pixel</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/209873106/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/712754008/detail.aspx</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5938,33 +5938,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>146</v>
+        <v>733</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном удлиненная</t>
+          <t>Видеокарта GTX 1070 8Gb Game Rock</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>314963410</v>
+        <v>706143236</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>DEPLAZA</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>DEPLAZA - одежда и аксессуары</t>
+          <t>ИП Попов Д.А.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/314963410/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/706143236/detail.aspx</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5976,33 +5976,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>147</v>
+        <v>736</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Куртка джинсовая</t>
+          <t>Видеокарта RTX 5060 8 ГБ RTL (NE75060S19P1-GB2063D)</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>321501057</v>
+        <v>703813046</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>NonHuman</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>VelvetGroup</t>
+          <t>EXPEcomp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/321501057/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/703813046/detail.aspx</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6014,33 +6014,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>148</v>
+        <v>737</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз короткая</t>
+          <t>Видеокарта GeForce RTX 5060 WINDFORCE, 8 ГБ GDDR7</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>142782359</v>
+        <v>703795326</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Eustera</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>EUSTERA</t>
+          <t>240km/h Market</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/142782359/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/703795326/detail.aspx</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6052,33 +6052,33 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>149</v>
+        <v>768</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном из экокожи</t>
+          <t>Видеокарта RX 580 8GB GDDR5 256bit HDMI 3DP PCIe оригинал</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>718893777</v>
+        <v>634570334</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>MathStyle</t>
+          <t>AFOX</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MathStyle</t>
+          <t>TENGRI STORE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/718893777/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/634570334/detail.aspx</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6090,33 +6090,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>150</v>
+        <v>771</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз экокожа</t>
+          <t>Видеокарта для пк Prime GeForce RTX 5070 12GB</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>363302634</v>
+        <v>618406197</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>STALIXO</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>STALIXO</t>
+          <t>НА СВЯЗИ</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/363302634/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/618406197/detail.aspx</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6128,33 +6128,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>151</v>
+        <v>772</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Куртка удлиненная с капюшоном весенняя</t>
+          <t>Видеокарта RTX5070 WINDFORCE OC SFF 12G (GV-N5070WF3OC-12GD)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>168759986</v>
+        <v>618244043</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Tutel Mekuty</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>femunique</t>
+          <t>NOMAD MARKET</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/168759986/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/618244043/detail.aspx</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6166,33 +6166,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>152</v>
+        <v>784</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Куртка спортивная мембранная демисезонная с капюшоном</t>
+          <t>Видеокарта GeForce RTX 5070 Ti GamingPro-S 16GB</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>231032403</v>
+        <v>608638956</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Reaktiv</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Reaktiv</t>
+          <t>Mirage</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/231032403/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/608638956/detail.aspx</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6204,33 +6204,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>153</v>
+        <v>787</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Куртка трансформер весенняя оверсайз</t>
+          <t>Видеокарта GIGABYTE GeForce RTX 5060 AERO OC 8G РФ</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>746040596</v>
+        <v>607602024</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>GOLT&amp;P</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GOLT&amp;P</t>
+          <t>GSM BUTIK</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/746040596/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/607602024/detail.aspx</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6242,33 +6242,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>154</v>
+        <v>789</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Куртка пальто демисезонная фуфайка стеганая "ВИРЖИНИЯ"</t>
+          <t>Видеокарта RTX 5060 8 ГБ RTL (GV-N5060WF2MAX OC-8GD)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>489445830</v>
+        <v>605522767</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>VARSAVVAS</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>VARSAVVAS</t>
+          <t>A1-Market</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/489445830/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/605522767/detail.aspx</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6280,33 +6280,33 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>155</v>
+        <v>790</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Куртка удлиненная демисезонная больших размеров на весну</t>
+          <t>Видеокарта Palit RTX 4060 STORMX 8 ГБ</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>180036592</v>
+        <v>600647036</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Мадам Макси</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>МАДАМ МАКСИ</t>
+          <t>Оригинальная техника</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/180036592/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/600647036/detail.aspx</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6318,33 +6318,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>156</v>
+        <v>792</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Куртка демисезонная больших размеров Парка с капюшоном</t>
+          <t>Видеокарта RX 9060 XT Challenger OC</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>740856474</v>
+        <v>598946765</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Louis Nesta</t>
+          <t>ASRock</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Louis Nesta</t>
+          <t>Fly Buy</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/740856474/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/598946765/detail.aspx</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6356,33 +6356,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>157</v>
+        <v>830</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном</t>
+          <t>Видеокарта GEFORCE RTX 5060 Twin EDGE</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>782016604</v>
+        <v>581084474</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>GOOGKAEVA</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>GOOGKAEVA</t>
+          <t>Cyber shop</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/782016604/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/581084474/detail.aspx</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6394,33 +6394,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>158</v>
+        <v>831</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>куртка короткая зимняя из экокожи</t>
+          <t>Видеокарта PULSE Radeon RX 9070 16G</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>47787057</v>
+        <v>579561168</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>La Laine</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>La Laine</t>
+          <t>LEPRO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/47787057/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/579561168/detail.aspx</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6432,33 +6432,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>159</v>
+        <v>836</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Куртка зимняя удлиненная с капюшоном</t>
+          <t>Видеокарта NVIDIA GeForce RTX 5070 GAMING TRIO OC 12 ГБ</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>312800141</v>
+        <v>572843066</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>D Angelo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>SokolStore</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/312800141/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/572843066/detail.aspx</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6470,33 +6470,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>160</v>
+        <v>838</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Бомбер куртка оверсайз драповая демисезонная</t>
+          <t>Видеокарта GTX 1080 8gb GDDR5X GameRock</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>180525120</v>
+        <v>567813038</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>emse</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ООО МП Макс</t>
+          <t>Народная Электроника</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/180525120/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/567813038/detail.aspx</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6508,33 +6508,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>161</v>
+        <v>879</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Куртка зимняя короткая с капюшоном</t>
+          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (N506T2-16D7X-191073N)</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>244137516</v>
+        <v>556474865</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Caste</t>
+          <t>Inno3D</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CASTE</t>
+          <t>Modern Device</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/244137516/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/556474865/detail.aspx</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6546,33 +6546,33 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>162</v>
+        <v>894</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Куртка с капюшоном двухзамковая молния</t>
+          <t>Видеокарта RTX 5080 Gaming OC, 16 ГБ</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>197950250</v>
+        <v>549179611</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Мисс Данин</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>МИСС ДАНИН-Зара</t>
+          <t>NDS - Оригинальные товары с гарантией</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/197950250/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/549179611/detail.aspx</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6584,33 +6584,33 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>163</v>
+        <v>905</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Куртка весенняя с капюшоном стеганая</t>
+          <t>Видеокарта NVIDIA GeForce GTX 1650 4GB GDDR6</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>756938717</v>
+        <v>534403802</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>You SPECIAL</t>
+          <t>KFA2</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>YOU SPECIAL</t>
+          <t>Компьютерная техника РФ</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/756938717/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/534403802/detail.aspx</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6622,33 +6622,33 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>164</v>
+        <v>912</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Куртка демисезонная кимоно пиджак</t>
+          <t>Видеокарта RTX5080 16GB PA-RTX5080 GAMINGPRO OC 16GB</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>473437377</v>
+        <v>524551091</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2211 GATE</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ВЕСЬ АССОРТИМЕНТ МАГАЗИНА</t>
+          <t>Getsy</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473437377/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/524551091/detail.aspx</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6660,33 +6660,33 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>165</v>
+        <v>915</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Куртка демисезонная оверсайз короткая</t>
+          <t>Видеокарта MSI Geforce RTX 3050 LP OC</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>792930800</v>
+        <v>518253497</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>I'M UNIQUE</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>I'M UNIQUE</t>
+          <t>TOO 1WN TRADE</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/792930800/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/518253497/detail.aspx</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6698,33 +6698,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>166</v>
+        <v>919</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном оверсайз удлиненная</t>
+          <t>Топовая игровая видеокарта RTX 3070 8gb</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>783844206</v>
+        <v>507196279</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>warmark</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>warmark</t>
+          <t>Gamer Place</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/783844206/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/507196279/detail.aspx</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6736,33 +6736,33 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>167</v>
+        <v>920</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Куртка с капюшоном короткая</t>
+          <t>Видеокарта GeForce RTX 5050 Twin Edge</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>518243844</v>
+        <v>504252794</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sundelica</t>
+          <t>ZOTAC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sundelica Fashion</t>
+          <t>Fly Buy</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/518243844/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/504252794/detail.aspx</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6774,33 +6774,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>168</v>
+        <v>927</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Куртка демисезонная бомбер замшевая</t>
+          <t>Видеокарта Gigabyte GeForce GTX 1080 Ti AORUS 11264MB</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>466612290</v>
+        <v>498785578</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KATY PRETTY</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KATYPRETTY</t>
+          <t>Народная Электроника</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/466612290/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/498785578/detail.aspx</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6812,33 +6812,33 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>169</v>
+        <v>937</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Куртка демисезонная с капюшоном удлиненная</t>
+          <t>Видеокарта RTX5060 DUAL OC 8G (NE75060S19P1-GB2063D)</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>734683556</v>
+        <v>452564789</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>URBANDO</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pommy аксессуары</t>
+          <t>TerraBit</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/734683556/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/452564789/detail.aspx</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6850,33 +6850,33 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>170</v>
+        <v>938</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Куртка весенняя больших размеров</t>
+          <t>Видеокарта (GV-N5060OC-8GL) RTX5060 OC Low Profile 8G</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>140460979</v>
+        <v>452564773</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LESANTO</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>LESANTO</t>
+          <t>TerraBit</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/140460979/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/452564773/detail.aspx</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6888,33 +6888,33 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>171</v>
+        <v>943</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Куртка пуховик зимняя с натуральным мехом песца</t>
+          <t>Видеокарта Intel Arc B580 Milestone 12G GDDR6 192bit/2670Mhz</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>459735414</v>
+        <v>447112423</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SAFINA MODA</t>
+          <t>Maxsun</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SAFINA</t>
+          <t>КомпьютерМаркет</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/459735414/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/447112423/detail.aspx</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6926,33 +6926,33 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>172</v>
+        <v>957</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Куртка джинсовая оверсайз</t>
+          <t>Видеокарта RADEON RX 6600 M 8GB GDDR6 игровая (rx6600m)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>225770542</v>
+        <v>443827286</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AMLA FASHION</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AMLA FASHION</t>
+          <t>REMHATEK</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/225770542/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/443827286/detail.aspx</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6964,33 +6964,33 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>173</v>
+        <v>958</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Куртка прямая короткая стеганая демисезонная</t>
+          <t>Видеокарта PCI-E 4.0 GV-R64D6-4GL AMD Radeon RX 6400 4096Mb</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>659377551</v>
+        <v>440704713</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>LaWinter</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ТОРГЛАЙН</t>
+          <t>ТЕХНОВСЁ</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/659377551/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/440704713/detail.aspx</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7002,33 +7002,33 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>174</v>
+        <v>962</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Куртка демисезонная весенняя 2026 с капюшоном</t>
+          <t>Видеокарта для пк RX 9060XT 8ГБ GDDR6 игровая</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>530983574</v>
+        <v>437801601</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Po.Li</t>
+          <t>Gigabyte</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Po.Li</t>
+          <t>Позитроника</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/530983574/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/437801601/detail.aspx</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7040,33 +7040,33 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>175</v>
+        <v>975</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Куртка демисезонная удлиненная с капюшоном и поясом</t>
+          <t>Видеокарта TUF GAMING Radeon RX 9070 XT OC Edition 16 ГБ</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>770629089</v>
+        <v>428886626</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kardani</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>KARDANI</t>
+          <t>Omni Market</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/770629089/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/428886626/detail.aspx</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7078,2696 +7078,36 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Куртки</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>176</v>
+        <v>977</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Двусторонняя весенняя фуфайка куртка стеганная</t>
+          <t>Видеокарта RTX5060Ti INFINITY 3 NV RTX 5060TI 16Gb Черный</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>496974992</v>
+        <v>423954883</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Nurbelek</t>
+          <t>Palit</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nurbelek</t>
+          <t>ЭЛЕКТРОНИКА</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/496974992/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/423954883/detail.aspx</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>177</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная с капюшоном</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>781678790</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Лунный свет</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>MoonLove</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/781678790/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>178</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная с капюшоном</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>744076445</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>MAXFAME</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>MAXFAME</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/744076445/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>179</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Удлиненная куртка оверсайз и парка с капюшоном зимняя</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>261788201</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>MY EPIC LOVE</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>MY EPIC LOVE</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/261788201/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>180</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Куртка с капюшоном</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>621960737</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>ICETEC</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>ИП Киреева Д.В.</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/621960737/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>181</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Куртка утепленная женская водоотталкивающая с капюшоном</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>712580133</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Outventure</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>ООО Спортмастер</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/712580133/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>182</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная короткая жилетка трансформер</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>732659428</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>LANN</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>LANN</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/732659428/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>183</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>куртка демисезонная больших размеров с капюшоном</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>321076602</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Woolf</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Woolf</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/321076602/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>184</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Весенняя куртка женская</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>527814487</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>SOK</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>SOK</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/527814487/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>185</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Пальто шерстяное оверсайз длинное</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>553855452</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Rozova collection</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Rozova collection</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/553855452/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>186</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Куртка бомбер чебурашка экошуба</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>174641679</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>модная одежда</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>МОДНАЯ ОДЕЖДА</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/174641679/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>187</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Куртка кожаная косуха</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>390988555</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>СИН Sinsay</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>FES retail</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/390988555/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>188</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Куртка с капюшоном демисезонная парка приталенная</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>460568493</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>RIPE BRUSNI4KA</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Коллекция Весна 2026</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/460568493/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>189</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная удлиненная стеганая с шарфом</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>439978589</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>PipShale</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Каталог PipShale</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/439978589/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>190</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Куртка без капюшона оверсайз демисезонная</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>147879920</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Joinse</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Joinse</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/147879920/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>191</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Удлиненная куртка демисезонная с капюшоном и кулиской парка</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>456805173</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>LUNEWE</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Morllie</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/456805173/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>192</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Куртка джинсовая оверсайз</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>153561002</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>FADJO</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>FADJO</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/153561002/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>193</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная стеганая</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>498119495</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Misiz23</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/498119495/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>194</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Куртка косуха с меховой отделкой эко-кожа</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>253185139</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Jan Steen</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>ТM Jan Steen</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/253185139/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>195</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Короткая куртка полупальто демисезонная утепленная</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>356870949</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>SAINT SIN</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>SAINT SIN</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/356870949/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>196</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная стеганая</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>458332084</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>KEYCONNECT</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>АNNA GRAKOVA</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/458332084/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>197</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Куртка укороченная весенняя ветровка стеганая на пуговицах</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>710369234</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Lanicka</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>LANICKA</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/710369234/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>198</v>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Удлиненная куртка с капюшоном на запах с поясом зимняя</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>51443546</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Levitate</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Хоум Брендс</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/51443546/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>199</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Куртка пуховик оверсайз с капюшоном зимняя</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>498089365</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>DeaVia</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>DeaVia</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/498089365/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>200</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Куртка парка весна удлиненная оверсайз с капюшоном</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>756315880</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>T&amp;Clothes</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>T&amp;Clothes</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/756315880/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>201</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Куртка весенняя с поясом удлиненная</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>687525556</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>KSF</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>KSF</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/687525556/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>202</v>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Куртка кожаная демисезонная с капюшоном больших размеров</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>171550899</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>BRADLY</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>BRADLY</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/171550899/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>203</v>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная длинная с капюшоном</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>246509259</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>BERDJOLI</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>BERDJOLI</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/246509259/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>204</v>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Куртка с капюшоном</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>832867864</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Dorimodes-style</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>DesireDream</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/832867864/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>205</v>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Синяя джинсовая куртка</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>228510279</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Feimailis</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>ИП Чернецкая А. С.</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/228510279/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>206</v>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Куртка весенняя 2026 с капюшоном парка удлиненная</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>727222388</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Kravchenko</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>SvetLine</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/727222388/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>207</v>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная больших размеров plus size с капюшоном</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>475661891</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>lalook</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>lalook</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/475661891/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>208</v>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Куртка пиджак замшевая демисезонная</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>324320290</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>MOREWARM</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Morewarm</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/324320290/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>209</v>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Куртка зимняя с капюшоном короткая</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>261973653</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>VAU Look</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>VAU Look</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/261973653/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>210</v>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Куртка зимняя оверсайз с капюшоном удлиненная</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>248392790</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>NKIM</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>N’KIM</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/248392790/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>211</v>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная кимоно с поясом</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>804364676</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>BoChikWear</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>BoChikWear</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/804364676/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>212</v>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная женская оверсайз из искусственного меха</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>478311943</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>OHARA</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Магазин верхней одежды</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/478311943/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>213</v>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная оверсайз</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>313666768</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>birdy</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>BIRDY</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/313666768/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>214</v>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Куртка рубашка стеганая демисезонная</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>398915171</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>ZUZO</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>ZUZO</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/398915171/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>215</v>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Зимняя куртка длинная с капюшоном</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>523387105</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>RESHKA studio</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>RESHKA</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/523387105/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>216</v>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Демисезонная курта большие размеры с капюшоном</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>342610364</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AngelLily</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>AngelLily</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/342610364/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>217</v>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Зимняя куртка оверсайз с капюшоном</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>595542763</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>MFQ</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>ТПК</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/595542763/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>218</v>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Куртка зимняя оверсайз</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>256267410</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>NUDE SHOP</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>NUDE SHOP</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/256267410/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>219</v>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная с капюшоном oversize</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>686652330</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>OKSANA UTOVA BRAND</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>OKSANA UTOVA BRAND</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/686652330/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>220</v>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная удлиненная больших размеров</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>212142805</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>laVici</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Store Art</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/212142805/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>221</v>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Демисезонная куртка y2k оверсайз на осень</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>268152034</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Korean style store</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Y2KSpark</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/268152034/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>222</v>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Косуха кожаная куртка демисезон кожанка большие размеры</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>327996644</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>MALIWEAR</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>MALIWEAR</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/327996644/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>223</v>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная черная</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>316816781</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Velecy</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>ИП Велисевич</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/316816781/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>224</v>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная короткая</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>313792043</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Beautyfornia Ladies Boutique</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Качественные товары со скидкой до 85%</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/313792043/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>225</v>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Куртки/Женские куртки</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>200704196</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Damira fashion</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Damira</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/200704196/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>226</v>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Куртка джинсовая большие размеры</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>209650762</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>BIGGEST</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>BIGGEST</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/209650762/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>227</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная с капюшоном оверсайз</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>319978630</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>iDiLiS CLO</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>ИП Ижаев Ю.В.</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/319978630/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>228</v>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная утепленная удлиненная с капюшоном</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>152712325</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Xbs</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>XBS</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/152712325/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>229</v>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Куртка весенняя с капюшоном парка удлиненная</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>793564306</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Девочки хотят</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Взяла и заказала</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/793564306/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>230</v>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная стеганая удлиненная</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>475758791</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>BLICK YOU</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Blick Style</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/475758791/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>231</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Куртка зимняя вельветовая</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>271222124</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>ТЫСЯЧА СТОЛИЦ</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>ТЫСЯЧА СТОЛИЦ PRETTY</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/271222124/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>232</v>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Куртка замшевая весенняя</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>822338471</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>LOOVA</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>TRI-IMPULSE</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/822338471/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>233</v>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Куртка замшевая сафари демисезонная</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>784656154</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>BAUDA</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>BAUDA</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/784656154/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>234</v>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Куртка джинсовая оверсайз джинсовка</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>374093766</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Trendsetter Á Multibrand</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/374093766/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>235</v>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Бомбер демисезонный куртка оверсайз</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>789481293</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Boganga</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>BOGANGA</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/789481293/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>236</v>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Куртка лаковая короткая демисезонная</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>489535758</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>MISSNATAVI</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>MISSNATAVI</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/489535758/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>237</v>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>куртка демисезонная с капюшоном оверсайз короткая</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>171150540</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>ДИОМАНТ</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>ДИОМАНТ</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/171150540/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>238</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Куртка женская стеганая фуфайка весенняя</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>315798893</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Veveya</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Veveya</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/315798893/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>239</v>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Трендовая винтажная куртка замшевая с регулируемым капюшоном</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>446912989</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Mimora</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Mimora</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/446912989/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>240</v>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная удлиненная с капюшоном больших размеров</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>316011036</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Yarmarka palto</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Ярмарка пальто</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/316011036/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>241</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Куртка на запах оверсайз кимоно</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>508532697</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>SeeMe</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Посмотреть другие товары со скидкой</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/508532697/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>242</v>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Куртка весенняя больших размеров</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>161846291</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>SOLENDAY</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>SOLENDAY</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/161846291/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>243</v>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Пуховик зимний оверсайз короткий еврозима, воротник-стойка</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>712072909</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>ТЕЛОДВИЖЕНИЯ</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>ООО СКВТ</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/712072909/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>244</v>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Куртка парка удлиненная больших размеров</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>241832254</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>TIMEYARD</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>TIMEYARD</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/241832254/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>245</v>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Куртка демисезонная стёганая укороченная с поясом</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>249292603</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>BVy Whattowear</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>BVy Whattowear</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/249292603/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>READY_FOR_RESEARCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Куртки</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>246</v>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Куртка весенняя</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>767140640</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Envoke</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>ИП Козлов А. В.</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/767140640/detail.aspx</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
         <is>
           <t>READY_FOR_RESEARCH</t>
         </is>

--- a/output/research_sample.xlsx
+++ b/output/research_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -474,25 +474,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 12 ГБ RTL (RTX 5070 12G SHADOW 2X OC)</t>
+          <t>Куртка весенняя с капюшоном длинная</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>355329855</v>
+        <v>502380099</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>La VIO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>La VIO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/355329855/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502380099/detail.aspx</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -512,25 +512,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070 XT Challenger</t>
+          <t>Куртка парка зимняя с капюшоном</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>781591963</v>
+        <v>492302848</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASRock</t>
+          <t>SOFO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lumono</t>
+          <t>SOFO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/781591963/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/492302848/detail.aspx</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -550,25 +550,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 Ti 16 ГБ RTL (GV-N507TWF3OCV2-16GD)</t>
+          <t>Куртка весна с капюшоном удлиненная демисезонная</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>706673918</v>
+        <v>144678759</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>STEFRIMI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>STEFRIMI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/706673918/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/144678759/detail.aspx</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -588,25 +588,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Видеокарта для пк RTX 5070 12ГБ GDDR7 WINDFORCE OC SFF</t>
+          <t>Куртка женская демисезонная тонкая с капюшоном весна</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>393771530</v>
+        <v>172327837</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>DAYCLO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>СИТИЛИНК</t>
+          <t>DAYCLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/393771530/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/172327837/detail.aspx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -618,33 +618,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RTX 5090 TUF GAMING 32 ГБ (TUF-RTX5090-32G-GAMING)</t>
+          <t>Куртка кожаная косуха весенняя</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>823111536</v>
+        <v>144680877</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Gouter</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Продавец</t>
+          <t>Fashion Design</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/823111536/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/144680877/detail.aspx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -656,33 +656,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 Twin Edge</t>
+          <t>Куртка весенняя удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>784893688</v>
+        <v>203625366</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>SHAYLY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lumono</t>
+          <t>SHAYLY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/784893688/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/203625366/detail.aspx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -694,33 +694,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti GAMING TRIO OC 16 ГБ (RTX 5070 Ti 16G GAMING TRI…</t>
+          <t>Куртка демисезонная стеганая удлиненная с капюшоном Пальто</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>823110325</v>
+        <v>118177975</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>VASHLOOK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Продавец</t>
+          <t>VASHLOOK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/823110325/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/118177975/detail.aspx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -732,33 +732,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (NE7506TS19T1-GB2061S)</t>
+          <t>Куртка</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>527449656</v>
+        <v>185222392</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>USEREZHI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>USEREZHI УСЕРЁЖИ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/527449656/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/185222392/detail.aspx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -770,33 +770,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti EAGLE OC ICE SFF 16 ГБ (GV-N507TEAGLEOC ICE-16GD)</t>
+          <t>Куртка демисезонная стеганая</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>565713653</v>
+        <v>155897954</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Продавец</t>
+          <t>ООО МАГИЯПАЛЬТО</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/565713653/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/155897954/detail.aspx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -808,33 +808,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RTX 5080 GAMINGPRO OC 16 ГБ (NE75080S19T2-GB2031A)</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>560729608</v>
+        <v>663131053</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>MUNIRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Продавец</t>
+          <t>MUNIRA collection</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/560729608/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/663131053/detail.aspx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -846,33 +846,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9060XT 16 ГБ RTL (90YV0LG2-M0NA00)</t>
+          <t>Куртка демисезонная стеганая с поясом</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>705837299</v>
+        <v>36304301</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>VAMPONI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>VAMPONI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/705837299/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/36304301/detail.aspx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -884,33 +884,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Ti TWIN X2</t>
+          <t>Куртка кожаная пиджак косуха</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>737258396</v>
+        <v>143610231</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>KONVY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chaban Base</t>
+          <t>KONVY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/737258396/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/143610231/detail.aspx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -922,33 +922,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Видеокарта для пк RTX 5080 16ГБ GDDR7 DLSS игровая</t>
+          <t>Куртка демисезонная оверсайз с капюшоном весна</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>399733754</v>
+        <v>458514779</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>by LuLu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>СИТИЛИНК</t>
+          <t>by LuLu</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/399733754/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/458514779/detail.aspx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -960,33 +960,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070XT 16 ГБ RTL (DP.Z4FWW.P01)</t>
+          <t>Весенняя куртка длинная</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>676209794</v>
+        <v>97202282</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Acer</t>
+          <t>Magpie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>Magpie</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/676209794/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/97202282/detail.aspx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -998,33 +998,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti WINDFORCE OC SFF 16 ГБ (GV-N507TWF3OC-16GD)</t>
+          <t>Куртка стеганая демисезонная с капюшоном и поясом</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>560709672</v>
+        <v>431054122</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>LAROI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
+          <t>LAROI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/560709672/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/431054122/detail.aspx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1036,33 +1036,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RTX 5070 Twin Edge 12 ГБ (ZT-B50700E-10P)</t>
+          <t>Куртка демисезонная больших размеров с капюшоном</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>578723918</v>
+        <v>171325115</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>AvantaC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ООО "ПРОМ-ЭНЕРГО"</t>
+          <t>HadMart</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/578723918/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/171325115/detail.aspx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1074,33 +1074,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Ti 16GB TWIN X2</t>
+          <t>Кожаная куртка для женщин демисезон с капюшоном</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>725979824</v>
+        <v>341378733</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>Bless You Today</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PC City</t>
+          <t>Bless You</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/725979824/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/341378733/detail.aspx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1112,33 +1112,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Видеокарта Geforce RTX 5060 Ti TWIN X2</t>
+          <t>Куртка на осень короткая оверсайз</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>611984887</v>
+        <v>314963479</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>POLAIR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cyber shop</t>
+          <t>POLAIR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/611984887/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/314963479/detail.aspx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1150,33 +1150,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Видеокарта ROG Astral GeForce RTX 5080 OC 16GB GDDR7</t>
+          <t>Куртка с эко-норкой и капюшоном</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>781957564</v>
+        <v>596709668</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Ladyexclusive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TDX</t>
+          <t>Ladyexclusive</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/781957564/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/596709668/detail.aspx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1188,33 +1188,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5080 16G VENTUS 3X OC</t>
+          <t>Куртка стеганая демисезонная женская</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>323039306</v>
+        <v>314703133</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>TIMAMI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Getsy</t>
+          <t>TIMAMI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/323039306/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/314703133/detail.aspx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1226,33 +1226,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RX 9060 XT PURE OC 16 ГБ (11350-02-20G)</t>
+          <t>Куртка женская весна с капюшоном</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>564311113</v>
+        <v>207655137</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>iNeed</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
+          <t>iNeed &amp; IRONSIDE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/564311113/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/207655137/detail.aspx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1264,33 +1264,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060TI INFINITY 3 OC 16ГБ GDDR7 4608 ядер</t>
+          <t>Демисезонная куртка с мехом утепленная</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>687118968</v>
+        <v>182543456</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Fasonika</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>СИТИЛИНК</t>
+          <t>BOGERA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/687118968/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/182543456/detail.aspx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1302,33 +1302,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Видеокарта ROG Astral GeForce RTX 5080 OC 16GB GDDR7</t>
+          <t>Куртка демисезонная удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>781806874</v>
+        <v>506319884</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Virton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IT-D</t>
+          <t>VIRTON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/781806874/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/506319884/detail.aspx</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1340,33 +1340,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (ZT-B50620E-10M)</t>
+          <t>Куртка с замшевой фактурой утепленная без капюшона</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>526625042</v>
+        <v>733931399</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>Befree</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>MELON FASHION GROUP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/526625042/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/733931399/detail.aspx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1378,33 +1378,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RX 9070 XT NITRO+ OC 16 ГБ (11348-01-20G)</t>
+          <t>Куртка-пуховик зимняя парка с мехом и капюшоном</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>823110282</v>
+        <v>256204207</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>LUXINE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Продавец</t>
+          <t>Женская одежда LUXINE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/823110282/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/256204207/detail.aspx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1416,33 +1416,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RTX 5070 GamingPro-S 12 ГБ (NE75070019K9-GB2050U)</t>
+          <t>Куртка весенняя удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>560720133</v>
+        <v>699575812</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>PULMOND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
+          <t>PULMOND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/560720133/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/699575812/detail.aspx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1454,33 +1454,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5080 16 ГБ RTL (GV-N5080AERO OC-16GD)</t>
+          <t>Куртка кожаная женская большие размеры</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>502308708</v>
+        <v>202323739</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Noelle sharm</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gigabyte Official Store</t>
+          <t>Noelle sharm</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/502308708/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/202323739/detail.aspx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1492,33 +1492,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070 XT GAMING OC 16G, 16 Гб GDDR6 UltraHD</t>
+          <t>Весенняя куртка короткая</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>445280948</v>
+        <v>436675245</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>LOTS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getsy</t>
+          <t>LOTS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/445280948/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/436675245/detail.aspx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1530,33 +1530,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070 GAMING OC 16G, 16 Гб GDDR6</t>
+          <t>Куртка демисезонная парка удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>445318305</v>
+        <v>246763829</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>SIIRA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Omni Market</t>
+          <t>SIIRA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/445318305/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/246763829/detail.aspx</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1568,33 +1568,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 8G SHADOW 2X OC MAX</t>
+          <t>Куртка демисезонная стеганая с капюшоном и поясом</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>814743980</v>
+        <v>697127524</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>BONOMI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>BONOMI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/814743980/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/697127524/detail.aspx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1606,33 +1606,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Infinity 3 OC 12GB GDDR7</t>
+          <t>Куртка женская демисезонная большие размеры осень</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>597161650</v>
+        <v>86497379</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Kera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TDX</t>
+          <t>Женская одежда Kera и детская одежда Пиколино</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/597161650/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/86497379/detail.aspx</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1644,33 +1644,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 WHITE OC 12GB PALIT</t>
+          <t>Куртка демисезонная укороченная утепленная</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>762389768</v>
+        <v>458311484</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Bemansa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Надо брать!</t>
+          <t>Bemansa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/762389768/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/458311484/detail.aspx</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1682,33 +1682,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5080 X3 OC</t>
+          <t>Куртка демисезонная</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>790818747</v>
+        <v>120163258</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>ZAVATORIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lumono</t>
+          <t>ZAVATORIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/790818747/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/120163258/detail.aspx</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1720,33 +1720,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5080 16 ГБ RTL (GV-N5080AORUSM ICE-16GD)</t>
+          <t>Куртка с поясом демисезонная удлиненная</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>502308696</v>
+        <v>500314245</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AORUS</t>
+          <t>Vera Nicco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>Vera Nicco</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/502308696/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/500314245/detail.aspx</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1758,33 +1758,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti Battle AX DUO 16 ГБ (RTX 5060 Ti Battle AX DUO 16GB-V)</t>
+          <t>Куртка экокожа косуха пиджак</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>729250187</v>
+        <v>200620484</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colorful</t>
+          <t>AM&amp;PA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
+          <t>AM&amp;PA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/729250187/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/200620484/detail.aspx</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1796,33 +1796,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Видеокарта ASUS GeForce RTX 5070 12 ГБ GDDR7 Prime</t>
+          <t>Куртка демисезонная короткая с капюшоном</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>723151906</v>
+        <v>712835789</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>MSstyle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BestRAM</t>
+          <t>MSstyle</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/723151906/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/712835789/detail.aspx</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1834,33 +1834,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Игровая видеокарта AMD Radeon RX 580 8Gb GDDR5 RX580 8 Гб</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>164656358</v>
+        <v>473034287</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JieShuo</t>
+          <t>Lofajoy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>COSMO-V</t>
+          <t>LOFAJOY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/164656358/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473034287/detail.aspx</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1872,33 +1872,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Видеокарта AMD Radeon RX 9070 Challenger 16GB</t>
+          <t>Куртка демисезонная с капюшоном оверсайз</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>817479717</v>
+        <v>768371423</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASRock</t>
+          <t>Eberron</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>Eberron</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/817479717/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/768371423/detail.aspx</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1910,33 +1910,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RTX 5060 iCraft AIGA OC 8 ГБ (MS-RTX5060 iCraft OC8G AIGA)</t>
+          <t>Куртка тонкая демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>766403735</v>
+        <v>807017929</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maxsun</t>
+          <t>Sofiny</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ООО "ЛИДЕР ДИСТРИБУЦИИ"</t>
+          <t>SOFINY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/766403735/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/807017929/detail.aspx</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1948,33 +1948,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PELADN GeForce RTX 3060 Ti 8GB ARMOUR</t>
+          <t>Куртка весенняя удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>689196268</v>
+        <v>338330063</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>BYSHU</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>To gamers from a gamer</t>
+          <t>BYSHU</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/689196268/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/338330063/detail.aspx</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1986,33 +1986,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Видеокарта Asus E3504U-C DUAL- GEFORCE RTX5060-8G</t>
+          <t>Куртка женская демисезон с капюшоном натуральный мех</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>704884457</v>
+        <v>142254839</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>RUTE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Techno Bisal</t>
+          <t>ПЕРЕЙТИ В КАТАЛОГ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/704884457/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/142254839/detail.aspx</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2024,33 +2024,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Видеокарта 5060 VENTUS 3X OC</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>738949384</v>
+        <v>355829416</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>SONAME STUDIO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Яратон</t>
+          <t>SONAME studio</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/738949384/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/355829416/detail.aspx</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2062,33 +2062,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Ti SHADOW 3X OC, 16 ГБ</t>
+          <t>Куртка длинная зимняя с капюшоном</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>482977120</v>
+        <v>100911533</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>GAINRUSANOV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>240km/h Market</t>
+          <t>GAINRUSANOV</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/482977120/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/100911533/detail.aspx</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2100,33 +2100,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9060XT 16 ГБ RTL (11350-03-20G)</t>
+          <t>Куртка весенняя парка с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>757417447</v>
+        <v>795165595</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>By BUtton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>By BUtton</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/757417447/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/795165595/detail.aspx</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2138,33 +2138,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Dual Fan</t>
+          <t>Весенняя куртка стеганая</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>668899409</v>
+        <v>533380570</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PNY</t>
+          <t>LawBeauty</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Железный Король</t>
+          <t>MARMAT</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/668899409/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/533380570/detail.aspx</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2176,33 +2176,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Видеокарта Intel Arc B580 iCraft 12G</t>
+          <t>Стеганая куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>531846287</v>
+        <v>305979107</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maxsun</t>
+          <t>Tyne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Magdevice</t>
+          <t>Tyne</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/531846287/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/305979107/detail.aspx</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2214,33 +2214,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GeForce GTX 1660 SUPER VENTUS XS OC 6GB Игровая</t>
+          <t>Двусторонняя весенняя фуфайка куртка стеганная женская</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>156549910</v>
+        <v>314241736</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>Nurbelek</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>To gamers from a gamer</t>
+          <t>МУСУРАЛИЕВА Д.Н.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/156549910/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/314241736/detail.aspx</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2252,33 +2252,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Видеокарта GEFORCE RTX 5070 12GB OC</t>
+          <t>Куртка демисезонная с капюшоном весенняя большие размеры</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>850804121</v>
+        <v>772423972</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PNY</t>
+          <t>Acalypha</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Хайтек Плюс</t>
+          <t>Acalypha</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/850804121/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/772423972/detail.aspx</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2290,33 +2290,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070 XT OC 16GB GDDR6 ASUS TUF Gaming Radeon</t>
+          <t>Куртка демисезонная кимоно пиджак</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>832353082</v>
+        <v>719653546</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Zunelle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FUJILAB</t>
+          <t>Zunelle</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/832353082/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/719653546/detail.aspx</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2328,33 +2328,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>157</v>
+        <v>51</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 12 ГБ (NE75070019K9-GB2050U)</t>
+          <t>Куртка весенняя удлиненная оверсайз с капюшоном</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>760667535</v>
+        <v>721247735</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Positive Mind</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>HONEY GLOW</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/760667535/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/721247735/detail.aspx</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2366,33 +2366,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Видеокарта AMD Radeon RX 9070 XT Prime OC White 16 ГБ</t>
+          <t>Куртка демисезонная на запах с поясом</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>571277020</v>
+        <v>332614606</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>SHATILOVA M.V.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>SHATILOVA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/571277020/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/332614606/detail.aspx</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2404,33 +2404,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Видеокарта Radeon RX9070 XT OC 16Gb TUF-RX9070XT-O16G-GAMING</t>
+          <t>Кожаная куртка на кулиске оверсайз</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>543916044</v>
+        <v>460447909</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>BLUMONE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ХОЛОДИЛЬНИК.ру</t>
+          <t>BLUMONE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/543916044/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460447909/detail.aspx</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2442,33 +2442,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 12G DUAL OC, 12 ГБ GDDR7 UltraHD</t>
+          <t>Куртка демисезонная с капюшоном стеганая</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>451820702</v>
+        <v>504904986</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>RUMOUR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Getsy</t>
+          <t>Ромашка</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/451820702/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/504904986/detail.aspx</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2480,33 +2480,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>193</v>
+        <v>55</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Видеокарта NVIDIA GeForce RTX 5060 Shadow 2X OC</t>
+          <t>Куртка весенняя бомбер с капюшоном утепленный</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>538357893</v>
+        <v>316934243</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>ELZAZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hard Comp</t>
+          <t>NSWEAR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/538357893/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/316934243/detail.aspx</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2518,33 +2518,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Видеокарта игровая для пк TUF Gaming GeForce RTX 5070 12GB</t>
+          <t>Джинсовая куртка удлиненная стрейч</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>618427434</v>
+        <v>200735882</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ЕСЦ</t>
+          <t>EKATERINA FEDRES - производитель с 2001г.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/618427434/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/200735882/detail.aspx</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2556,33 +2556,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Видеокарта MSI RTX 5060 Ti 8G VENTUS 3X OC</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>608357604</v>
+        <v>795221669</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>YOUONE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AWSD</t>
+          <t>ВЗВ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/608357604/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/795221669/detail.aspx</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2594,33 +2594,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5080 GamingPro</t>
+          <t>Куртка демисезонная с поясом и капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>815251970</v>
+        <v>172283339</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>JULI PITON</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>МультиБренд</t>
+          <t>JULI PITON</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/815251970/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/172283339/detail.aspx</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2632,33 +2632,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>211</v>
+        <v>59</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9070 16GB GV-R9070GAMING OC-16GD</t>
+          <t>Куртка демисезонная весна парка с капюшоном</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>542394046</v>
+        <v>316610837</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Jenny Poletty</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>Jenny Poletty</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/542394046/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/316610837/detail.aspx</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2670,33 +2670,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GeForce GTX 1660 SUPER 6GB GDDR6</t>
+          <t>Куртка весенняя удлиненная стройнит</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>538270698</v>
+        <v>172231945</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PelaDN</t>
+          <t>Lisa Bella</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IKARD</t>
+          <t>LisaBella</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/538270698/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/172231945/detail.aspx</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2708,33 +2708,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Видеокарта NVIDIA GeForce RTX 5060 Infinity 3 OC 8 ГБ</t>
+          <t>Куртка демисезонная удлиненная с капюшоном весна</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>758526174</v>
+        <v>316275211</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>MOOX</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ElectroTron</t>
+          <t>МООХ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/758526174/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/316275211/detail.aspx</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2746,33 +2746,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>229</v>
+        <v>62</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Видеокарта PCI-E 4.0 RTX3050-O6G-LP-BRK NV RTX3050 6Gb 96bit</t>
+          <t>Куртка демисезонная парка с капюшоном</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>377359826</v>
+        <v>467762621</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Leoni Aoki</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>СИТИЛИНК</t>
+          <t>Leoni Aoki</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/377359826/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/467762621/detail.aspx</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2784,33 +2784,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Видеокарта 5080 ARGB EPIC-X RGB OC Triple Fan GPU</t>
+          <t>Куртка демисезонная больших размеров с капюшоном</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>656934759</v>
+        <v>720961971</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PNY</t>
+          <t>La Zelia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cyber shop</t>
+          <t>La Zelia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/656934759/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/720961971/detail.aspx</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2822,33 +2822,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Видеокарта для ПК Radeon RX 5500 XT 8 гб GDDR6 игровая новая</t>
+          <t>Куртка демисезонная короткая стеганая ветровка с капюшоном</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>835633478</v>
+        <v>146354941</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PelaDN</t>
+          <t>MulluMix</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ViaBit</t>
+          <t>MulluMix Fashion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/835633478/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/146354941/detail.aspx</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2860,33 +2860,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>241</v>
+        <v>65</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce GTX 750 Ti 4GB</t>
+          <t>Куртка короткая</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>495629076</v>
+        <v>198656127</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Clozer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RedGoosePC</t>
+          <t>Clozer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/495629076/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/198656127/detail.aspx</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2898,33 +2898,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 3070 Ti 8GB GDDR6 AMOUR</t>
+          <t>Куртка оверсайз демисезонная утепленная с капюшоном</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>694269149</v>
+        <v>306170378</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SELFIE SHOP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>To gamers from a gamer</t>
+          <t>SELFIE SHOP &amp; BROKSTONE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/694269149/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/306170378/detail.aspx</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2936,33 +2936,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Ti 16 GB Infinity 3 OC</t>
+          <t>Куртка демисезонная короткая с капюшоном оверсайз</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>839564791</v>
+        <v>462993870</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Unigou</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marlen</t>
+          <t>UNIGOU</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/839564791/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/462993870/detail.aspx</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2974,33 +2974,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>271</v>
+        <v>68</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Ti Infinity 3 16GB GDDR7</t>
+          <t>Удлиненная стеганая куртка</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>758185742</v>
+        <v>330934054</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>FROGMAN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>IT-D</t>
+          <t>Butique</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/758185742/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/330934054/detail.aspx</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3012,33 +3012,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>272</v>
+        <v>69</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5050 8GB RTX 5050 8G SHADOW 2X OC MSI</t>
+          <t>Куртка демисезонная парка удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>762759860</v>
+        <v>699884583</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>VERLENTA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Надо брать!</t>
+          <t>ИП Шумакова</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/762759860/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/699884583/detail.aspx</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3050,33 +3050,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>285</v>
+        <v>70</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 WINDFORCE OC 8G</t>
+          <t>Куртка кожаная с мехом демисезонная утепленная</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>633482563</v>
+        <v>765127124</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Fali</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Яратон</t>
+          <t>Fali</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/633482563/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/765127124/detail.aspx</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3088,33 +3088,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>286</v>
+        <v>71</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Dual OC</t>
+          <t>Пиджак стеганый куртка жакет фуфайка</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>788498445</v>
+        <v>355086944</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>MokoLo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lumono</t>
+          <t>MokoLo</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/788498445/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/355086944/detail.aspx</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3126,33 +3126,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Видеокарта GEFORCE RTX 5070 12GB OC</t>
+          <t>Куртка кожаная короткая стеганая</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>814985975</v>
+        <v>174093208</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PNY</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>МультиБренд</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/814985975/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/174093208/detail.aspx</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3164,33 +3164,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>290</v>
+        <v>73</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 8GB Infinity 2 OC</t>
+          <t>Весенняя куртка демисезонная больших размеров</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>850804026</v>
+        <v>732466710</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>ELMARI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Хайтек Плюс</t>
+          <t>ELMARI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/850804026/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/732466710/detail.aspx</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3202,33 +3202,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>293</v>
+        <v>74</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Видеокарта PALIT RTX5060 INFINITY 2 OC 8GB</t>
+          <t>Куртка зимняя с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>742580902</v>
+        <v>246127195</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gigabyte GeForce</t>
+          <t>NiceJune</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Telenova</t>
+          <t>NJ TOP</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/742580902/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/246127195/detail.aspx</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3240,33 +3240,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>298</v>
+        <v>75</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Игровая видеокарта JieShuo RX 580 8gb</t>
+          <t>Джинсовая куртка с капюшоном</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>649742483</v>
+        <v>217682337</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Cersi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PELADN Official Store</t>
+          <t>Cersi</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/649742483/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/217682337/detail.aspx</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3278,33 +3278,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Radeon RX 6600 XT 8GB GDDR6 (rx6600xt)</t>
+          <t>Куртка бомбер с капюшоном демисезонная</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>310585167</v>
+        <v>250110394</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>UMO SHOP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ElectroRon</t>
+          <t>UMO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/310585167/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/250110394/detail.aspx</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3316,33 +3316,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Ti Windforce 16GB GDDR7</t>
+          <t>Куртка демисезонная оверсайз стеганая легкая пуховая</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>776182946</v>
+        <v>692819565</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>BULMER</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>TDX</t>
+          <t>Bulmer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/776182946/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/692819565/detail.aspx</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3354,33 +3354,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 WHITE OC</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>837573178</v>
+        <v>756244179</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>OffCold</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Яратон</t>
+          <t>Комфорт</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/837573178/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/756244179/detail.aspx</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3392,33 +3392,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Radeon RX 5500XT 8GD 8ГБ GDDR6 (RX5500XT) игровая BLACK-RED</t>
+          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>195487503</v>
+        <v>760835247</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Mare Blanco</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>To gamers from a gamer</t>
+          <t>Maré Blanco</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/195487503/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/760835247/detail.aspx</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3430,33 +3430,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Видеокарта для пк игровая GeForce RTX 5070TI Eagle 16Gb</t>
+          <t>Куртка демисезонная с капюшоном короткая</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>584504104</v>
+        <v>251610433</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>MARUZE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ЭлМир</t>
+          <t>MaruZE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/584504104/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/251610433/detail.aspx</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3468,33 +3468,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Видеокарта Graphiccard R7-350 (PCI-E 3.0 2 GB GDDR5)</t>
+          <t>Куртка зимняя с капюшоном оверсайз</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>542565225</v>
+        <v>268947499</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALAINIX</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>YOffice</t>
+          <t>ALAINIX</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/542565225/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/268947499/detail.aspx</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3506,33 +3506,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 3060 12 ГБ RTL (AF3060-12GD6H7-V4)</t>
+          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>757417679</v>
+        <v>678700723</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AFOX</t>
+          <t>GLAUREN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>GLAUREN</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/757417679/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/678700723/detail.aspx</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3544,33 +3544,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Видеокарта RX580 8GB (RX 580 8ГБ) 2048SP</t>
+          <t>Куртка демисезонная оверсайз</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>560755558</v>
+        <v>721141997</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>XFX</t>
+          <t>ROCK-LAB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>To gamers from a gamer</t>
+          <t>ROCK-LAB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/560755558/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/721141997/detail.aspx</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3582,33 +3582,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Видеокарта игровая PALIT Geforce rtx 3070 8gb</t>
+          <t>Куртка демисезонная удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>786203236</v>
+        <v>753224837</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WINDYCOATS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PELADN Official Store</t>
+          <t>Одежда и товары для комфортной жизни</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/786203236/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/753224837/detail.aspx</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3620,33 +3620,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>376</v>
+        <v>85</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Видеокарта Radeon RX7600 OC</t>
+          <t>Куртка весенняя с капюшоном оверсайз</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>787435795</v>
+        <v>728859616</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>My Gelato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lumono</t>
+          <t>Malachite</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/787435795/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/728859616/detail.aspx</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3658,33 +3658,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>377</v>
+        <v>86</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RTX 5070 DUAL OC 12 ГБ (DUAL-RTX5070-O12G)</t>
+          <t>Куртка весенняя кимоно с поясом</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>869172900</v>
+        <v>336912945</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>MILLYS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Мерлион</t>
+          <t>MILLYS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/869172900/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/336912945/detail.aspx</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3696,33 +3696,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>381</v>
+        <v>87</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 2060 6 ГБ RTL (NK206FG66F)</t>
+          <t>Куртка демисезонная парка с капюшоном удлиненная на кулиске</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>781067134</v>
+        <v>744166513</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ninja (Sinotex)</t>
+          <t>ZEKKA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>Zekka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/781067134/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/744166513/detail.aspx</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3734,33 +3734,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>394</v>
+        <v>88</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Видеокарта Dual GeForce RTX 5060 OC</t>
+          <t>Куртка весенняя удлиненная больших размеров с капюшоном</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>600970110</v>
+        <v>758272149</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>DORELIA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fly Buy</t>
+          <t>ALKONDA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/600970110/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/758272149/detail.aspx</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3772,33 +3772,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>398</v>
+        <v>89</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Twin X2</t>
+          <t>Куртка ветровка с поясом и капюшоном демисезонная легкая</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>772866212</v>
+        <v>148954022</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>Vlasova</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Яратон</t>
+          <t>ИП Огнев</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/772866212/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/148954022/detail.aspx</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3810,33 +3810,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 3070 8ГБ (NF307FG86F)</t>
+          <t>Куртка женская демисезонная</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>173461586</v>
+        <v>262218128</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SINOTEX</t>
+          <t>Rosabella</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/173461586/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/262218128/detail.aspx</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3848,33 +3848,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>406</v>
+        <v>91</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 GAMING Twin Edge OC</t>
+          <t>Куртка демисезонная короткая</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>841454452</v>
+        <v>732991342</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>MONAPURE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Яратон</t>
+          <t>MONAPURE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/841454452/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/732991342/detail.aspx</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3886,33 +3886,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>412</v>
+        <v>92</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Видеокарта Gunnir Arc A580 Index 8 ГБ GDDR6 HDMI</t>
+          <t>Куртка весенняя с капюшоном больших размеров</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>593694089</v>
+        <v>174113381</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GUNNIR</t>
+          <t>Freedom shop</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Скорость ПК</t>
+          <t>Freedom shop</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/593694089/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/174113381/detail.aspx</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3924,33 +3924,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>423</v>
+        <v>93</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 3070 Gaming 8Gb</t>
+          <t>Куртка на кулиске весенняя</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>762675367</v>
+        <v>502648560</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>MOLLO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Чип Дейли</t>
+          <t>Nurova</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/762675367/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502648560/detail.aspx</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3962,33 +3962,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>424</v>
+        <v>94</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Видеокарта WINDFORCE MAX OC 8Gb GEFORCE RTX 5060</t>
+          <t>Куртка демисезонная больших размеров</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>764884571</v>
+        <v>25846173</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>STYLE MC CLASSIC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Techno Bisal</t>
+          <t>STYLE MC CLASSIC</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/764884571/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/25846173/detail.aspx</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4000,33 +4000,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>429</v>
+        <v>95</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Python III</t>
+          <t>Куртка демисезонная укороченная утепленная с капюшоном</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>804283800</v>
+        <v>247644567</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gainward</t>
+          <t>Miletti</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Diplay</t>
+          <t>DeaMILETTI</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/804283800/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/247644567/detail.aspx</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4038,33 +4038,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>433</v>
+        <v>96</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Мощная игровая видеокарта для компьютера ASUS RX 580 8GB</t>
+          <t>Куртка демисезонная с капюшоном короткая</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>768067518</v>
+        <v>734218253</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>SEREBRYX</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PELADN Official Store</t>
+          <t>Кальмиус</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/768067518/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/734218253/detail.aspx</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4076,33 +4076,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>440</v>
+        <v>97</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Игровая видеокарта NVIDIA GeForce GTX 1060 DUAL 6G белая</t>
+          <t>Куртка демисезонная парка с капюшоном утепленная</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>415291929</v>
+        <v>460270627</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>MERAQVIN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Компьютерная техника РФ</t>
+          <t>АН</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/415291929/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460270627/detail.aspx</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4114,33 +4114,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>441</v>
+        <v>98</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 Ti Eagle Max OC 16GB GDDR7</t>
+          <t>Куртка демисезонная больших размеров</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>583695370</v>
+        <v>209651656</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>PUVILDRA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IT-D</t>
+          <t>Be in fashion</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/583695370/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/209651656/detail.aspx</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4152,33 +4152,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>442</v>
+        <v>99</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti INFINITY 3 16 ГБ (NE7506T019T1-GB2061S)</t>
+          <t>Куртка пиджак весенняя стежка с поясом черная</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>869172843</v>
+        <v>204535569</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Reprise</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Мерлион</t>
+          <t>Женская одежда</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/869172843/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/204535569/detail.aspx</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4190,33 +4190,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>463</v>
+        <v>100</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Игровая видеокарта для пк GeForce GT 730 4GB</t>
+          <t>Куртка демисезонная парка с капюшоном</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>471058531</v>
+        <v>734083997</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atermiter</t>
+          <t>Lofel</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Acs Quality</t>
+          <t>LOFEL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/471058531/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/734083997/detail.aspx</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4228,33 +4228,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>469</v>
+        <v>101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 AERO OC 8GB (GV-N5060AERO OC-8GD)</t>
+          <t>Куртка демисезонная с капюшоном стеганая</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>501135388</v>
+        <v>387424622</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>EL'MAGIC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ХОЛОДИЛЬНИК.ру</t>
+          <t>ЭЛЬ'МЭЙДЖИК / EL'MAGIC</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/501135388/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/387424622/detail.aspx</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4266,33 +4266,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>473</v>
+        <v>102</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce GTX 1050 TI 4 ГБ</t>
+          <t>Куртка бомбер кожаная оверсайз</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>477997053</v>
+        <v>492564098</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>Moroz Brand</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>GameWork</t>
+          <t>Moroz brand</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/477997053/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/492564098/detail.aspx</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4304,33 +4304,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>474</v>
+        <v>103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5080 WINDFORCE OC SFF 16G</t>
+          <t>Куртка весенняя с рукавом реглан</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>822706561</v>
+        <v>343281349</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Binitra Bini</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Салонсвязи.ру</t>
+          <t>Binitra Bini</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/822706561/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/343281349/detail.aspx</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4342,33 +4342,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>483</v>
+        <v>104</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RTX 5070 INSPIRE 3X OC 12 ГБ (RTX 5070 12G INSPIRE 3X OC)</t>
+          <t>Куртка бомбер демисезонная</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>869172845</v>
+        <v>710194493</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>ТВОЕ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Мерлион</t>
+          <t>ТВОЕ</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/869172845/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/710194493/detail.aspx</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4380,33 +4380,33 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>493</v>
+        <v>105</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Видеокарта ASUS GeForce RTX 5060 Dual OC Edition</t>
+          <t>Куртка стеганая больших размеров демисезонная</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>518253901</v>
+        <v>102576166</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>ASTEXVEL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TOO 1WN TRADE</t>
+          <t>ASTEXVEL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/518253901/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/102576166/detail.aspx</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4418,33 +4418,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>510</v>
+        <v>106</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Видеокарта Sapphire PCI-E 4.0 11314-07-20G RX 6500XT Gaming</t>
+          <t>Куртка демисезонная короткая</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>541496803</v>
+        <v>247455605</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>ANOLTA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>СИТИЛИНК</t>
+          <t>А.С</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/541496803/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/247455605/detail.aspx</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4456,33 +4456,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>516</v>
+        <v>107</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Игровая Видеокарта для ПК NVIDIA GeForce GTX 1050 Ti OC 4G</t>
+          <t>Куртка демисезонная больших размеров с капюшоном</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>435632786</v>
+        <v>317820717</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Luxury Plus</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Компьютерная техника РФ</t>
+          <t>Luxury Plus</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/435632786/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/317820717/detail.aspx</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4494,33 +4494,33 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>517</v>
+        <v>108</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Видеокарта для ПК NVIDIA GeForce GTX 1050 Ti с Подсветкой</t>
+          <t>Куртка на пуху демисезонная</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>415277124</v>
+        <v>496472475</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>fameForce</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Компьютерная техника РФ</t>
+          <t>FameForce</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/415277124/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/496472475/detail.aspx</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4532,33 +4532,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>518</v>
+        <v>109</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 GAMING TRIO OC, 12 ГБ GDDR7, 8K</t>
+          <t>Куртка демисезонная с капюшоном больших размеров</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>445266087</v>
+        <v>327487633</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>Милледи</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Omni Market</t>
+          <t>Милледи</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/445266087/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/327487633/detail.aspx</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4570,33 +4570,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>520</v>
+        <v>110</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Видеокарта игровая RTX 5070 GamingPro-S 12ГБ GDDR7</t>
+          <t>Удлиненная куртка парка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>449793252</v>
+        <v>753846707</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>RAMORE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Позитроника</t>
+          <t>RAMORE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/449793252/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/753846707/detail.aspx</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4608,33 +4608,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>531</v>
+        <v>111</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 SOLID</t>
+          <t>Куртка короткая с капюшоном демисезонная</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>725753242</v>
+        <v>169746779</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>HOLODILOV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RAGATSHOP</t>
+          <t>ИП Холодилова А.С.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/725753242/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/169746779/detail.aspx</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4646,33 +4646,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Dual OC</t>
+          <t>Куртка больших размеров кожаная тренч</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>736017853</v>
+        <v>206104869</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Sharming Style</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Железный Король</t>
+          <t>Sharming Style</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/736017853/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/206104869/detail.aspx</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4684,33 +4684,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>540</v>
+        <v>113</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Видеокарта Asrock RX 5500 XT Challenger D OC 8Гб GDDR6</t>
+          <t>Куртка весенняя с капюшоном больших размеров</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>214439465</v>
+        <v>495869567</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ASRock</t>
+          <t>Gratia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Laztorg</t>
+          <t>Moodgirls</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/214439465/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/495869567/detail.aspx</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4722,33 +4722,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>556</v>
+        <v>114</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Видеокарта для ПК NVIDIA GeForce GTX1050Ti StormX 4G</t>
+          <t>Стеганая куртка демисезонная удлиненная</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>435208093</v>
+        <v>455499423</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>DEES</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Компьютерная техника РФ</t>
+          <t>Магазин</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/435208093/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/455499423/detail.aspx</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4760,33 +4760,33 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>558</v>
+        <v>115</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Игровая видеокарта Colorful GTX 1660 Super Battle-Ax</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>753842221</v>
+        <v>453526855</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Colorful</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DELISE</t>
+          <t>SV Fashion</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/753842221/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/453526855/detail.aspx</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4798,33 +4798,33 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>564</v>
+        <v>116</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Видеокарта Radeon RX 5700 XT 8GB GDDR6 (rx5700xt)8гб игровая</t>
+          <t>Джинсовка бомбер с капюшоном оверсайз</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>434638230</v>
+        <v>340633288</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JieShuo</t>
+          <t>LEONALOVE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>REMHATEK</t>
+          <t>LEONALOVE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/434638230/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/340633288/detail.aspx</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4836,33 +4836,33 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>565</v>
+        <v>117</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Видеокарта Radeon RX 5500 8GB GDDR6 (rx5500 8gb)</t>
+          <t>Куртка весенняя с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>447965373</v>
+        <v>744318538</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SALVIA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>REMHATEK</t>
+          <t>Salvia</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/447965373/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/744318538/detail.aspx</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4874,33 +4874,33 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>572</v>
+        <v>118</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Видеокарта AMD Radeon 9070 Challenger</t>
+          <t>Куртка больших размеров весенняя</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>927404155</v>
+        <v>441463601</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ASRock</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Бутик спорта</t>
+          <t>AiSofia</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/927404155/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/441463601/detail.aspx</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4912,33 +4912,33 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>573</v>
+        <v>119</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5090 GAMING TRIO OC</t>
+          <t>Куртка демисезонная с капюшоном на весну</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>927401883</v>
+        <v>530958151</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>SAMULIN</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Бутик спорта</t>
+          <t>SAMULIN</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/927401883/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/530958151/detail.aspx</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4950,33 +4950,33 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>575</v>
+        <v>120</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Видеокарта Palit GeForce RTX 5080 GamingPro</t>
+          <t>Куртка демисезонная с капюшоном парка</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>907354129</v>
+        <v>753396582</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MOMNALI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ПРОФСВЯЗЬ-РО</t>
+          <t>E.N.V. Brand</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/907354129/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/753396582/detail.aspx</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4988,33 +4988,33 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>576</v>
+        <v>121</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Видеокарта Prime GeForce RTX 5070 Ti 16 ГБ GDDR7 OC</t>
+          <t>Тёплая женская куртка с воротником</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>881370678</v>
+        <v>758116829</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Zolla</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BestRAM</t>
+          <t>Zolla</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/881370678/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/758116829/detail.aspx</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5026,33 +5026,33 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>584</v>
+        <v>122</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti EAGLE OC ICE SFF 16 ГБ (GV-N507TEAGLEOC ICE-16GD…</t>
+          <t>Куртка весенняя с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>869172860</v>
+        <v>456472357</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>MONOMIR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Мерлион</t>
+          <t>MONOMIR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/869172860/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456472357/detail.aspx</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5064,33 +5064,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>594</v>
+        <v>123</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 3050 StormX 6ГБ</t>
+          <t>Куртка демисезонная оверсайз</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>867286101</v>
+        <v>597021892</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>LuMini Style</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Digital.zone</t>
+          <t>LuMini</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/867286101/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/597021892/detail.aspx</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5102,33 +5102,33 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>596</v>
+        <v>124</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GeForce RTX 5070 Infinity 3 OC [NE75070S19K9-GB2050S]</t>
+          <t>Куртка демисезонная короткая</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>853333396</v>
+        <v>763730369</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Trend product</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Finest Gadgets</t>
+          <t>Все товары</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/853333396/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/763730369/detail.aspx</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5140,33 +5140,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>606</v>
+        <v>125</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Видеокарта GEFORCE RTX 5070 INFINITY 3 12 GB GDDR7</t>
+          <t>Куртка рабочего женская тренд</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>828887045</v>
+        <v>471096415</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Verh</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Techno Bisal</t>
+          <t>Verh</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/828887045/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/471096415/detail.aspx</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5178,33 +5178,33 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>618</v>
+        <v>126</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Ti 8G VENTUS 3X OC</t>
+          <t>Куртка весенняя короткая стеганая с мехом</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>820619229</v>
+        <v>173306811</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>Ezewika</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Салонсвязи.ру</t>
+          <t>Ezewika</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/820619229/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/173306811/detail.aspx</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5216,33 +5216,33 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>625</v>
+        <v>127</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Видеокарта PCI-E GIGABYTE P104-100 MINING 8192MB GDDR5Х 8ГБ</t>
+          <t>Куртка демисезонная с капюшоном и поясом</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>820347294</v>
+        <v>248266222</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ZHENECHKA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ЮЛИКС</t>
+          <t>Женечка</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/820347294/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/248266222/detail.aspx</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5254,33 +5254,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>628</v>
+        <v>128</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Видеокарта GTX 1660 SUPER (GV-N166SD6-6GD) 6Гб GDDR6</t>
+          <t>Куртка пуховик с капюшоном зимний</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>815890622</v>
+        <v>443658277</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Modjimoda</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>Modjimoda</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/815890622/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/443658277/detail.aspx</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5292,33 +5292,33 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>631</v>
+        <v>129</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Видеокарта ASUS Radeon RX 9070 XT TUF GAMING OC</t>
+          <t>Куртка стеганая удлиненная осень с капюшоном</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>815341363</v>
+        <v>174898626</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Мисс Данин</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mirage</t>
+          <t>Мисс Данин</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/815341363/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/174898626/detail.aspx</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5330,33 +5330,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>634</v>
+        <v>130</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AMD Radeon 9060 XT GAMING OC</t>
+          <t>Куртка весенняя стёганая с капюшоном</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>809327694</v>
+        <v>727681195</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>LuBvi.brand</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mirage</t>
+          <t>LubVi.brand(ЛюбВи.бренд)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/809327694/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/727681195/detail.aspx</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5368,33 +5368,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>636</v>
+        <v>131</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5060 Dual OC 8 ГБ (NE75060S19P1-GB2063D)</t>
+          <t>Куртка весенняя парка удлиненная оверсайз</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>807462489</v>
+        <v>719947363</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Sweet Season</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ХОБОТ ДОСТАВИТ</t>
+          <t>CELEBRATE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/807462489/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/719947363/detail.aspx</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5406,33 +5406,33 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>637</v>
+        <v>132</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ONIX LUMI Arc B580 GDDR6 OC 12GB</t>
+          <t>Куртка демисезонная больших размеров</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>795751124</v>
+        <v>490170063</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>EAST OCEAN</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TechBridgeUSA</t>
+          <t>EAST OCEAN</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/795751124/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/490170063/detail.aspx</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5444,33 +5444,33 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>638</v>
+        <v>133</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Видеокарта 12 Гб iGame GeForce RTX 3080 TI LHR Advanced OC-V</t>
+          <t>Куртка бомбер кожаный оверсайз</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>793419578</v>
+        <v>326905930</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colorful</t>
+          <t>BASIC LINE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ZET-SHOP</t>
+          <t>BASIC LINE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/793419578/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/326905930/detail.aspx</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5482,33 +5482,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>642</v>
+        <v>134</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Видеокарта Radeon RX 9060 XT 8 GB GDDR6 (DP.Z4UWW.P02)</t>
+          <t>Рубашка джинсовая оверсайз</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>783836186</v>
+        <v>235623846</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Acer</t>
+          <t>Feimailis</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Buyon</t>
+          <t>МС Джинс</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/783836186/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/235623846/detail.aspx</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5520,33 +5520,33 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>661</v>
+        <v>135</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Игровая видеокарта для пк rx 580 4GB GDDR5</t>
+          <t>Куртка рабочего оверсайз под замшу на кулиске</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>774593050</v>
+        <v>481852936</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MODERATOR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>santafe</t>
+          <t>MD официальный магазин</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/774593050/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481852936/detail.aspx</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5558,33 +5558,33 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>665</v>
+        <v>136</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Видеокарта AMD Radeon RX 9070 XT Predator Bifrost OC 16 ГБ</t>
+          <t>Куртка теплая оверсайз демисезонная</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>770954968</v>
+        <v>137342117</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Acer</t>
+          <t>ТЫСЯЧА СТОЛИЦ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>ТЫСЯЧА СТОЛИЦ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/770954968/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/137342117/detail.aspx</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5596,33 +5596,33 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>666</v>
+        <v>137</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Видеокарта GIGABYTE GAMING GeForce RTX 5060 Ti 16 ГБ</t>
+          <t>Куртка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>770587869</v>
+        <v>807800136</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MOKI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>BestRAM</t>
+          <t>DORIMODES</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/770587869/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/807800136/detail.aspx</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5634,33 +5634,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>667</v>
+        <v>138</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 4070 WINDFORCE 2X OC V2</t>
+          <t>Куртка демисезонная с капюшоном ультралегкая</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>767199140</v>
+        <v>495664343</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>PROSimple ПРОСимпл</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ElectroHome</t>
+          <t>Мой Мир</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/767199140/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/495664343/detail.aspx</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5672,33 +5672,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>687</v>
+        <v>139</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Видеокарта Zotac RTX 5070Ti Solid Sff 16Gb</t>
+          <t>Куртка демисезонная парка с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>762099961</v>
+        <v>689575236</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING</t>
+          <t>GLDELUXE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ЭЛЕКТРОНИКА</t>
+          <t>GLDELUXE</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/762099961/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/689575236/detail.aspx</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5710,33 +5710,33 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>688</v>
+        <v>140</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 SHADOW 2X OC 8 ГБ</t>
+          <t>Куртка демисезонная с капюшоном больших размеров</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>761096262</v>
+        <v>466639026</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>Lady S+</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>RG Electro</t>
+          <t>MP.seller</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/761096262/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/466639026/detail.aspx</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5748,33 +5748,33 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>704</v>
+        <v>141</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti INFINITY 3 OC 16 ГБ (NE7506TS19T1-GB2061S)</t>
+          <t>Куртка весенняя короткая стеганая большой размер</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>756488716</v>
+        <v>169645664</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Moonmart</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Digital Land</t>
+          <t>Right Choice</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/756488716/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/169645664/detail.aspx</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5786,33 +5786,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>709</v>
+        <v>142</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 TWIN X2</t>
+          <t>Куртка демисезонная удлиненная с капюшоном весна</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>740376129</v>
+        <v>825025741</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>DIONCE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tech Store</t>
+          <t>DIONCE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/740376129/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/825025741/detail.aspx</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5824,33 +5824,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>718</v>
+        <v>143</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5070 Ti WINDFORCE OC SFF 16 ГБ, RTL</t>
+          <t>Куртка весенняя с капюшоном удлиненная еврозима</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>726188990</v>
+        <v>214070993</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALPEX</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Прекрасная Техника</t>
+          <t>ALPEX</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/726188990/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/214070993/detail.aspx</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5862,33 +5862,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>722</v>
+        <v>144</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5080 WINDFORCE SFF 16 ГБ (GV-N5080WF3-16GD)</t>
+          <t>Куртка - парка демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>716330537</v>
+        <v>453891026</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Snow Belle</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NeoRim</t>
+          <t>SVOYAESTHETICA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/716330537/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/453891026/detail.aspx</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5900,33 +5900,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>726</v>
+        <v>145</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RX 9060 XT PULSE GAMING OC 8GB (11350-04-20G)</t>
+          <t>Куртка Полиция МВД</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>712754008</v>
+        <v>209873106</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>мвдформа</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pixel</t>
+          <t>МВД ФОРМА</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/712754008/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/209873106/detail.aspx</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5938,33 +5938,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>733</v>
+        <v>146</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Видеокарта GTX 1070 8Gb Game Rock</t>
+          <t>Куртка демисезонная с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>706143236</v>
+        <v>314963410</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>DEPLAZA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ИП Попов Д.А.</t>
+          <t>DEPLAZA - одежда и аксессуары</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/706143236/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/314963410/detail.aspx</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5976,33 +5976,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>736</v>
+        <v>147</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 8 ГБ RTL (NE75060S19P1-GB2063D)</t>
+          <t>Куртка джинсовая</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>703813046</v>
+        <v>321501057</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>NonHuman</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>EXPEcomp</t>
+          <t>VelvetGroup</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/703813046/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/321501057/detail.aspx</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6014,33 +6014,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>737</v>
+        <v>148</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5060 WINDFORCE, 8 ГБ GDDR7</t>
+          <t>Куртка демисезонная оверсайз короткая</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>703795326</v>
+        <v>142782359</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Eustera</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>240km/h Market</t>
+          <t>EUSTERA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/703795326/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/142782359/detail.aspx</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6052,33 +6052,33 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>768</v>
+        <v>149</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Видеокарта RX 580 8GB GDDR5 256bit HDMI 3DP PCIe оригинал</t>
+          <t>Куртка демисезонная удлиненная с капюшоном из экокожи</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>634570334</v>
+        <v>718893777</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AFOX</t>
+          <t>MathStyle</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TENGRI STORE</t>
+          <t>MathStyle</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/634570334/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/718893777/detail.aspx</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6090,33 +6090,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>771</v>
+        <v>150</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Видеокарта для пк Prime GeForce RTX 5070 12GB</t>
+          <t>Куртка демисезонная оверсайз экокожа</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>618406197</v>
+        <v>363302634</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>STALIXO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>НА СВЯЗИ</t>
+          <t>STALIXO</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/618406197/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/363302634/detail.aspx</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6128,33 +6128,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>772</v>
+        <v>151</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5070 WINDFORCE OC SFF 12G (GV-N5070WF3OC-12GD)</t>
+          <t>Куртка удлиненная с капюшоном весенняя</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>618244043</v>
+        <v>168759986</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Tutel Mekuty</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NOMAD MARKET</t>
+          <t>femunique</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/618244043/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/168759986/detail.aspx</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6166,33 +6166,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>784</v>
+        <v>152</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5070 Ti GamingPro-S 16GB</t>
+          <t>Куртка спортивная мембранная демисезонная с капюшоном</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>608638956</v>
+        <v>231032403</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mirage</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/608638956/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/231032403/detail.aspx</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6204,33 +6204,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>787</v>
+        <v>153</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Видеокарта GIGABYTE GeForce RTX 5060 AERO OC 8G РФ</t>
+          <t>Куртка трансформер весенняя оверсайз</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>607602024</v>
+        <v>746040596</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>GOLT&amp;P</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GSM BUTIK</t>
+          <t>GOLT&amp;P</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/607602024/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/746040596/detail.aspx</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6242,33 +6242,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>789</v>
+        <v>154</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 8 ГБ RTL (GV-N5060WF2MAX OC-8GD)</t>
+          <t>Куртка пальто демисезонная фуфайка стеганая "ВИРЖИНИЯ"</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>605522767</v>
+        <v>489445830</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>VARSAVVAS</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>A1-Market</t>
+          <t>VARSAVVAS</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/605522767/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/489445830/detail.aspx</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6280,33 +6280,33 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>790</v>
+        <v>155</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Видеокарта Palit RTX 4060 STORMX 8 ГБ</t>
+          <t>Куртка удлиненная демисезонная больших размеров на весну</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>600647036</v>
+        <v>180036592</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Мадам Макси</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Оригинальная техника</t>
+          <t>МАДАМ МАКСИ</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/600647036/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/180036592/detail.aspx</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6318,33 +6318,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>792</v>
+        <v>156</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Видеокарта RX 9060 XT Challenger OC</t>
+          <t>Куртка демисезонная больших размеров Парка с капюшоном</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>598946765</v>
+        <v>740856474</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ASRock</t>
+          <t>Louis Nesta</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fly Buy</t>
+          <t>Louis Nesta</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/598946765/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/740856474/detail.aspx</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6356,33 +6356,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>830</v>
+        <v>157</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Видеокарта GEFORCE RTX 5060 Twin EDGE</t>
+          <t>Куртка демисезонная удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>581084474</v>
+        <v>782016604</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>GOOGKAEVA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cyber shop</t>
+          <t>GOOGKAEVA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581084474/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/782016604/detail.aspx</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6394,33 +6394,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>831</v>
+        <v>158</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Видеокарта PULSE Radeon RX 9070 16G</t>
+          <t>куртка короткая зимняя из экокожи</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>579561168</v>
+        <v>47787057</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>La Laine</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>LEPRO</t>
+          <t>La Laine</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/579561168/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/47787057/detail.aspx</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6432,33 +6432,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>836</v>
+        <v>159</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Видеокарта NVIDIA GeForce RTX 5070 GAMING TRIO OC 12 ГБ</t>
+          <t>Куртка зимняя удлиненная с капюшоном</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>572843066</v>
+        <v>312800141</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D Angelo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SokolStore</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/572843066/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/312800141/detail.aspx</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6470,33 +6470,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>838</v>
+        <v>160</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Видеокарта GTX 1080 8gb GDDR5X GameRock</t>
+          <t>Бомбер куртка оверсайз драповая демисезонная</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>567813038</v>
+        <v>180525120</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>emse</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Народная Электроника</t>
+          <t>ООО МП Макс</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/567813038/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/180525120/detail.aspx</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6508,33 +6508,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>879</v>
+        <v>161</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5060 Ti 16 ГБ RTL (N506T2-16D7X-191073N)</t>
+          <t>Куртка зимняя короткая с капюшоном</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>556474865</v>
+        <v>244137516</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Inno3D</t>
+          <t>Caste</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Modern Device</t>
+          <t>CASTE</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/556474865/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/244137516/detail.aspx</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6546,33 +6546,33 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>894</v>
+        <v>162</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Видеокарта RTX 5080 Gaming OC, 16 ГБ</t>
+          <t>Куртка с капюшоном двухзамковая молния</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>549179611</v>
+        <v>197950250</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Мисс Данин</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NDS - Оригинальные товары с гарантией</t>
+          <t>МИСС ДАНИН-Зара</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/549179611/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/197950250/detail.aspx</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6584,33 +6584,33 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>905</v>
+        <v>163</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Видеокарта NVIDIA GeForce GTX 1650 4GB GDDR6</t>
+          <t>Куртка весенняя с капюшоном стеганая</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>534403802</v>
+        <v>756938717</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KFA2</t>
+          <t>You SPECIAL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Компьютерная техника РФ</t>
+          <t>YOU SPECIAL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/534403802/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/756938717/detail.aspx</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6622,33 +6622,33 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>912</v>
+        <v>164</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5080 16GB PA-RTX5080 GAMINGPRO OC 16GB</t>
+          <t>Куртка демисезонная кимоно пиджак</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>524551091</v>
+        <v>473437377</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>2211 GATE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Getsy</t>
+          <t>ВЕСЬ АССОРТИМЕНТ МАГАЗИНА</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/524551091/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473437377/detail.aspx</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6660,33 +6660,33 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>915</v>
+        <v>165</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Видеокарта MSI Geforce RTX 3050 LP OC</t>
+          <t>Куртка демисезонная оверсайз короткая</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>518253497</v>
+        <v>792930800</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>I'M UNIQUE</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>TOO 1WN TRADE</t>
+          <t>I'M UNIQUE</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/518253497/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/792930800/detail.aspx</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6698,33 +6698,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>919</v>
+        <v>166</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Топовая игровая видеокарта RTX 3070 8gb</t>
+          <t>Куртка демисезонная с капюшоном оверсайз удлиненная</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>507196279</v>
+        <v>783844206</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>warmark</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gamer Place</t>
+          <t>warmark</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/507196279/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/783844206/detail.aspx</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6736,33 +6736,33 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>920</v>
+        <v>167</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Видеокарта GeForce RTX 5050 Twin Edge</t>
+          <t>Куртка с капюшоном короткая</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>504252794</v>
+        <v>518243844</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ZOTAC</t>
+          <t>Sundelica</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fly Buy</t>
+          <t>Sundelica Fashion</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/504252794/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/518243844/detail.aspx</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6774,33 +6774,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>927</v>
+        <v>168</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Видеокарта Gigabyte GeForce GTX 1080 Ti AORUS 11264MB</t>
+          <t>Куртка демисезонная бомбер замшевая</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>498785578</v>
+        <v>466612290</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KATY PRETTY</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Народная Электроника</t>
+          <t>KATYPRETTY</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/498785578/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/466612290/detail.aspx</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6812,33 +6812,33 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>937</v>
+        <v>169</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5060 DUAL OC 8G (NE75060S19P1-GB2063D)</t>
+          <t>Куртка демисезонная с капюшоном удлиненная</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>452564789</v>
+        <v>734683556</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>URBANDO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>TerraBit</t>
+          <t>Pommy аксессуары</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/452564789/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/734683556/detail.aspx</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6850,33 +6850,33 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>938</v>
+        <v>170</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Видеокарта (GV-N5060OC-8GL) RTX5060 OC Low Profile 8G</t>
+          <t>Куртка весенняя больших размеров</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>452564773</v>
+        <v>140460979</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>LESANTO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>TerraBit</t>
+          <t>LESANTO</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/452564773/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/140460979/detail.aspx</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6888,33 +6888,33 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>943</v>
+        <v>171</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Видеокарта Intel Arc B580 Milestone 12G GDDR6 192bit/2670Mhz</t>
+          <t>Куртка пуховик зимняя с натуральным мехом песца</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>447112423</v>
+        <v>459735414</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Maxsun</t>
+          <t>SAFINA MODA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>КомпьютерМаркет</t>
+          <t>SAFINA</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/447112423/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/459735414/detail.aspx</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6926,33 +6926,33 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>957</v>
+        <v>172</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Видеокарта RADEON RX 6600 M 8GB GDDR6 игровая (rx6600m)</t>
+          <t>Куртка джинсовая оверсайз</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>443827286</v>
+        <v>225770542</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMLA FASHION</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>REMHATEK</t>
+          <t>AMLA FASHION</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/443827286/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/225770542/detail.aspx</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6964,33 +6964,33 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>958</v>
+        <v>173</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Видеокарта PCI-E 4.0 GV-R64D6-4GL AMD Radeon RX 6400 4096Mb</t>
+          <t>Куртка прямая короткая стеганая демисезонная</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>440704713</v>
+        <v>659377551</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>LaWinter</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ТЕХНОВСЁ</t>
+          <t>ТОРГЛАЙН</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/440704713/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/659377551/detail.aspx</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7002,33 +7002,33 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>962</v>
+        <v>174</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Видеокарта для пк RX 9060XT 8ГБ GDDR6 игровая</t>
+          <t>Куртка демисезонная весенняя 2026 с капюшоном</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>437801601</v>
+        <v>530983574</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Gigabyte</t>
+          <t>Po.Li</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Позитроника</t>
+          <t>Po.Li</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/437801601/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/530983574/detail.aspx</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7040,33 +7040,33 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>975</v>
+        <v>175</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Видеокарта TUF GAMING Radeon RX 9070 XT OC Edition 16 ГБ</t>
+          <t>Куртка демисезонная удлиненная с капюшоном и поясом</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>428886626</v>
+        <v>770629089</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Kardani</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Omni Market</t>
+          <t>KARDANI</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/428886626/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770629089/detail.aspx</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7078,36 +7078,2696 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Куртки</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>977</v>
+        <v>176</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Видеокарта RTX5060Ti INFINITY 3 NV RTX 5060TI 16Gb Черный</t>
+          <t>Двусторонняя весенняя фуфайка куртка стеганная</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>423954883</v>
+        <v>496974992</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Palit</t>
+          <t>Nurbelek</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ЭЛЕКТРОНИКА</t>
+          <t>Nurbelek</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/423954883/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/496974992/detail.aspx</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>177</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная с капюшоном</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>781678790</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Лунный свет</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>MoonLove</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/781678790/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>178</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная с капюшоном</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>744076445</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>MAXFAME</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>MAXFAME</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/744076445/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>179</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Удлиненная куртка оверсайз и парка с капюшоном зимняя</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>261788201</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>MY EPIC LOVE</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>MY EPIC LOVE</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/261788201/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>180</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Куртка с капюшоном</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>621960737</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ICETEC</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ИП Киреева Д.В.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/621960737/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>181</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Куртка утепленная женская водоотталкивающая с капюшоном</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>712580133</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Outventure</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ООО Спортмастер</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/712580133/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>182</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная короткая жилетка трансформер</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>732659428</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>LANN</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>LANN</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/732659428/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>183</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>куртка демисезонная больших размеров с капюшоном</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>321076602</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Woolf</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Woolf</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/321076602/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>184</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Весенняя куртка женская</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>527814487</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>SOK</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>SOK</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/527814487/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>185</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное оверсайз длинное</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>553855452</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Rozova collection</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Rozova collection</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/553855452/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>186</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Куртка бомбер чебурашка экошуба</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>174641679</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>модная одежда</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>МОДНАЯ ОДЕЖДА</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/174641679/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>187</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Куртка кожаная косуха</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>390988555</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>СИН Sinsay</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>FES retail</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/390988555/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>188</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Куртка с капюшоном демисезонная парка приталенная</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>460568493</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RIPE BRUSNI4KA</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Коллекция Весна 2026</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/460568493/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>189</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная удлиненная стеганая с шарфом</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>439978589</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>PipShale</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Каталог PipShale</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/439978589/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>190</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Куртка без капюшона оверсайз демисезонная</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>147879920</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Joinse</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Joinse</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/147879920/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>191</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Удлиненная куртка демисезонная с капюшоном и кулиской парка</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>456805173</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>LUNEWE</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Morllie</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/456805173/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>192</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Куртка джинсовая оверсайз</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>153561002</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>FADJO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>FADJO</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/153561002/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>193</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная стеганая</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>498119495</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Misiz23</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/498119495/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>194</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Куртка косуха с меховой отделкой эко-кожа</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>253185139</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Jan Steen</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ТM Jan Steen</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/253185139/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>195</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Короткая куртка полупальто демисезонная утепленная</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>356870949</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SAINT SIN</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SAINT SIN</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/356870949/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>196</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная стеганая</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>458332084</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>KEYCONNECT</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>АNNA GRAKOVA</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/458332084/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>197</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Куртка укороченная весенняя ветровка стеганая на пуговицах</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>710369234</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Lanicka</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>LANICKA</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/710369234/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>198</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Удлиненная куртка с капюшоном на запах с поясом зимняя</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>51443546</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Levitate</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Хоум Брендс</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/51443546/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>199</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Куртка пуховик оверсайз с капюшоном зимняя</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>498089365</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>DeaVia</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DeaVia</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/498089365/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>200</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Куртка парка весна удлиненная оверсайз с капюшоном</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>756315880</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>T&amp;Clothes</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>T&amp;Clothes</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/756315880/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>201</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Куртка весенняя с поясом удлиненная</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>687525556</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>KSF</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>KSF</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/687525556/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>202</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Куртка кожаная демисезонная с капюшоном больших размеров</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>171550899</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>BRADLY</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>BRADLY</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/171550899/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>203</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная длинная с капюшоном</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>246509259</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>BERDJOLI</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>BERDJOLI</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/246509259/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>204</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Куртка с капюшоном</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>832867864</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Dorimodes-style</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>DesireDream</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/832867864/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>205</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Синяя джинсовая куртка</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>228510279</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Feimailis</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ИП Чернецкая А. С.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/228510279/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>206</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Куртка весенняя 2026 с капюшоном парка удлиненная</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>727222388</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Kravchenko</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SvetLine</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/727222388/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>207</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная больших размеров plus size с капюшоном</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>475661891</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>lalook</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>lalook</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/475661891/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>208</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Куртка пиджак замшевая демисезонная</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>324320290</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>MOREWARM</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Morewarm</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/324320290/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>209</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Куртка зимняя с капюшоном короткая</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>261973653</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>VAU Look</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>VAU Look</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/261973653/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>210</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Куртка зимняя оверсайз с капюшоном удлиненная</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>248392790</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>NKIM</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>N’KIM</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/248392790/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>211</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная кимоно с поясом</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>804364676</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>BoChikWear</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>BoChikWear</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/804364676/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>212</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная женская оверсайз из искусственного меха</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>478311943</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>OHARA</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Магазин верхней одежды</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/478311943/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>213</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная оверсайз</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>313666768</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>birdy</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>BIRDY</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/313666768/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>214</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Куртка рубашка стеганая демисезонная</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>398915171</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ZUZO</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ZUZO</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/398915171/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>215</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Зимняя куртка длинная с капюшоном</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>523387105</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>RESHKA studio</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>RESHKA</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/523387105/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>216</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Демисезонная курта большие размеры с капюшоном</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>342610364</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AngelLily</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>AngelLily</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/342610364/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>217</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Зимняя куртка оверсайз с капюшоном</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>595542763</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>MFQ</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ТПК</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/595542763/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>218</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Куртка зимняя оверсайз</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>256267410</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>NUDE SHOP</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>NUDE SHOP</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/256267410/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>219</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная с капюшоном oversize</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>686652330</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>OKSANA UTOVA BRAND</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>OKSANA UTOVA BRAND</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/686652330/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>220</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная удлиненная больших размеров</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>212142805</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>laVici</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Store Art</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/212142805/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>221</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Демисезонная куртка y2k оверсайз на осень</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>268152034</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Korean style store</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Y2KSpark</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/268152034/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>222</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Косуха кожаная куртка демисезон кожанка большие размеры</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>327996644</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>MALIWEAR</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>MALIWEAR</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/327996644/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>223</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная черная</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>316816781</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Velecy</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ИП Велисевич</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/316816781/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>224</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная короткая</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>313792043</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Beautyfornia Ladies Boutique</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Качественные товары со скидкой до 85%</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/313792043/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>225</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Куртки/Женские куртки</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>200704196</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Damira fashion</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Damira</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/200704196/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>226</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Куртка джинсовая большие размеры</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>209650762</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>BIGGEST</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>BIGGEST</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/209650762/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>227</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная с капюшоном оверсайз</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>319978630</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>iDiLiS CLO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ИП Ижаев Ю.В.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/319978630/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>228</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная утепленная удлиненная с капюшоном</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>152712325</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Xbs</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>XBS</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/152712325/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>229</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Куртка весенняя с капюшоном парка удлиненная</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>793564306</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Девочки хотят</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Взяла и заказала</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/793564306/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>230</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная стеганая удлиненная</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>475758791</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>BLICK YOU</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Blick Style</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/475758791/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>231</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Куртка зимняя вельветовая</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>271222124</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ТЫСЯЧА СТОЛИЦ</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ТЫСЯЧА СТОЛИЦ PRETTY</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/271222124/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>232</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Куртка замшевая весенняя</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>822338471</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>LOOVA</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>TRI-IMPULSE</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/822338471/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>233</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Куртка замшевая сафари демисезонная</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>784656154</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>BAUDA</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>BAUDA</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/784656154/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>234</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Куртка джинсовая оверсайз джинсовка</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>374093766</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Trendsetter Á Multibrand</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/374093766/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>235</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Бомбер демисезонный куртка оверсайз</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>789481293</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Boganga</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>BOGANGA</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/789481293/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>236</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Куртка лаковая короткая демисезонная</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>489535758</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>MISSNATAVI</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>MISSNATAVI</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/489535758/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>237</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>куртка демисезонная с капюшоном оверсайз короткая</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>171150540</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>ДИОМАНТ</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ДИОМАНТ</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/171150540/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>238</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Куртка женская стеганая фуфайка весенняя</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>315798893</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Veveya</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Veveya</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/315798893/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>239</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Трендовая винтажная куртка замшевая с регулируемым капюшоном</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>446912989</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Mimora</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Mimora</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/446912989/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>240</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная удлиненная с капюшоном больших размеров</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>316011036</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Yarmarka palto</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Ярмарка пальто</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/316011036/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>241</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Куртка на запах оверсайз кимоно</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>508532697</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>SeeMe</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Посмотреть другие товары со скидкой</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/508532697/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>242</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Куртка весенняя больших размеров</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>161846291</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>SOLENDAY</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>SOLENDAY</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/161846291/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>243</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Пуховик зимний оверсайз короткий еврозима, воротник-стойка</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>712072909</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>ТЕЛОДВИЖЕНИЯ</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ООО СКВТ</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/712072909/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>244</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Куртка парка удлиненная больших размеров</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>241832254</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>TIMEYARD</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>TIMEYARD</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/241832254/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>245</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Куртка демисезонная стёганая укороченная с поясом</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>249292603</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>BVy Whattowear</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>BVy Whattowear</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/249292603/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>READY_FOR_RESEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Куртки</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>246</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Куртка весенняя</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>767140640</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Envoke</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>ИП Козлов А. В.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/767140640/detail.aspx</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
         <is>
           <t>READY_FOR_RESEARCH</t>
         </is>
